--- a/output/ARKK/02_Market_Value_Analysis_1_to_2.5pct/1_to_2.5pct_Market_Value_Data.xlsx
+++ b/output/ARKK/02_Market_Value_Analysis_1_to_2.5pct/1_to_2.5pct_Market_Value_Data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="597">
   <si>
     <t>Date</t>
   </si>
@@ -1759,6 +1759,24 @@
   </si>
   <si>
     <t>2025-08-25/2025-08-31</t>
+  </si>
+  <si>
+    <t>2025-09-01/2025-09-07</t>
+  </si>
+  <si>
+    <t>2025-09-08/2025-09-14</t>
+  </si>
+  <si>
+    <t>2025-09-15/2025-09-21</t>
+  </si>
+  <si>
+    <t>2025-09-22/2025-09-28</t>
+  </si>
+  <si>
+    <t>2025-09-29/2025-10-05</t>
+  </si>
+  <si>
+    <t>2025-10-06/2025-10-12</t>
   </si>
   <si>
     <t>ETF</t>
@@ -2150,7 +2168,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D567"/>
+  <dimension ref="A1:D573"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9021,10 +9039,10 @@
         <v>6785069253.38</v>
       </c>
       <c r="C491">
-        <v>31316735250.53</v>
+        <v>31300428802.54</v>
       </c>
       <c r="D491">
-        <v>21.66595336040072</v>
+        <v>21.67724057770543</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -10082,13 +10100,97 @@
         <v>45894</v>
       </c>
       <c r="B567">
-        <v>7369925503.28</v>
+        <v>12183722387.56</v>
       </c>
       <c r="C567">
-        <v>22623430018.15</v>
+        <v>37292528638.4</v>
       </c>
       <c r="D567">
-        <v>32.57651690025501</v>
+        <v>32.67067917463354</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4">
+      <c r="A568" s="2">
+        <v>45901</v>
+      </c>
+      <c r="B568">
+        <v>9442559674.280001</v>
+      </c>
+      <c r="C568">
+        <v>28487447469.48</v>
+      </c>
+      <c r="D568">
+        <v>33.14638731461033</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4">
+      <c r="A569" s="2">
+        <v>45908</v>
+      </c>
+      <c r="B569">
+        <v>13914231789.03</v>
+      </c>
+      <c r="C569">
+        <v>44468831947.31</v>
+      </c>
+      <c r="D569">
+        <v>31.28985219471612</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4">
+      <c r="A570" s="2">
+        <v>45915</v>
+      </c>
+      <c r="B570">
+        <v>13048924896.17</v>
+      </c>
+      <c r="C570">
+        <v>45111555471.73</v>
+      </c>
+      <c r="D570">
+        <v>28.92590326296186</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4">
+      <c r="A571" s="2">
+        <v>45922</v>
+      </c>
+      <c r="B571">
+        <v>12217984516.73</v>
+      </c>
+      <c r="C571">
+        <v>39273569367.08</v>
+      </c>
+      <c r="D571">
+        <v>31.10994165702543</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4">
+      <c r="A572" s="2">
+        <v>45929</v>
+      </c>
+      <c r="B572">
+        <v>11987529294.35</v>
+      </c>
+      <c r="C572">
+        <v>40760946266.92</v>
+      </c>
+      <c r="D572">
+        <v>29.40934986114053</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4">
+      <c r="A573" s="2">
+        <v>45936</v>
+      </c>
+      <c r="B573">
+        <v>11331908754.19</v>
+      </c>
+      <c r="C573">
+        <v>42784831942.32</v>
+      </c>
+      <c r="D573">
+        <v>26.48580873115738</v>
       </c>
     </row>
   </sheetData>
@@ -10098,7 +10200,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M567"/>
+  <dimension ref="A1:M573"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -10147,10 +10249,10 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>5941564.319999999</v>
+        <v>5941564.32</v>
       </c>
       <c r="C2">
-        <v>348709.76</v>
+        <v>348709.7600000001</v>
       </c>
       <c r="D2">
         <v>5.868989061116485</v>
@@ -10159,13 +10261,13 @@
         <v>2465294.26</v>
       </c>
       <c r="F2">
-        <v>41.49234321509458</v>
+        <v>41.49234321509457</v>
       </c>
       <c r="G2">
         <v>3127560.3</v>
       </c>
       <c r="H2">
-        <v>52.63866772378895</v>
+        <v>52.63866772378893</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -10276,19 +10378,19 @@
         <v>783701.7999999999</v>
       </c>
       <c r="D5">
-        <v>3.87136096270592</v>
+        <v>3.871360962705919</v>
       </c>
       <c r="E5">
         <v>8936589.649999999</v>
       </c>
       <c r="F5">
-        <v>44.14531689314961</v>
+        <v>44.1453168931496</v>
       </c>
       <c r="G5">
         <v>10523282</v>
       </c>
       <c r="H5">
-        <v>51.98332214414447</v>
+        <v>51.98332214414446</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -10317,19 +10419,19 @@
         <v>626961.4399999999</v>
       </c>
       <c r="D6">
-        <v>3.871360962705919</v>
+        <v>3.87136096270592</v>
       </c>
       <c r="E6">
         <v>7149271.720000001</v>
       </c>
       <c r="F6">
-        <v>44.14531689314961</v>
+        <v>44.14531689314962</v>
       </c>
       <c r="G6">
         <v>8418625.6</v>
       </c>
       <c r="H6">
-        <v>51.98332214414446</v>
+        <v>51.98332214414447</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -10358,19 +10460,19 @@
         <v>783701.7999999999</v>
       </c>
       <c r="D7">
-        <v>3.87136096270592</v>
+        <v>3.871360962705919</v>
       </c>
       <c r="E7">
         <v>8936589.649999999</v>
       </c>
       <c r="F7">
-        <v>44.14531689314961</v>
+        <v>44.1453168931496</v>
       </c>
       <c r="G7">
         <v>10523282</v>
       </c>
       <c r="H7">
-        <v>51.98332214414447</v>
+        <v>51.98332214414446</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -10399,19 +10501,19 @@
         <v>783701.7999999999</v>
       </c>
       <c r="D8">
-        <v>3.87136096270592</v>
+        <v>3.871360962705919</v>
       </c>
       <c r="E8">
         <v>8936589.649999999</v>
       </c>
       <c r="F8">
-        <v>44.14531689314961</v>
+        <v>44.1453168931496</v>
       </c>
       <c r="G8">
         <v>10523282</v>
       </c>
       <c r="H8">
-        <v>51.98332214414447</v>
+        <v>51.98332214414446</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -10440,19 +10542,19 @@
         <v>783701.7999999999</v>
       </c>
       <c r="D9">
-        <v>3.87136096270592</v>
+        <v>3.871360962705919</v>
       </c>
       <c r="E9">
         <v>8936589.649999999</v>
       </c>
       <c r="F9">
-        <v>44.14531689314961</v>
+        <v>44.1453168931496</v>
       </c>
       <c r="G9">
         <v>10523282</v>
       </c>
       <c r="H9">
-        <v>51.98332214414447</v>
+        <v>51.98332214414446</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -10481,19 +10583,19 @@
         <v>626961.4399999999</v>
       </c>
       <c r="D10">
-        <v>3.871360962705919</v>
+        <v>3.87136096270592</v>
       </c>
       <c r="E10">
         <v>7149271.720000001</v>
       </c>
       <c r="F10">
-        <v>44.14531689314961</v>
+        <v>44.14531689314962</v>
       </c>
       <c r="G10">
         <v>8418625.6</v>
       </c>
       <c r="H10">
-        <v>51.98332214414446</v>
+        <v>51.98332214414447</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -10519,7 +10621,7 @@
         <v>18076311.92</v>
       </c>
       <c r="C11">
-        <v>889199.9000000001</v>
+        <v>889199.9</v>
       </c>
       <c r="D11">
         <v>4.919144479998551</v>
@@ -10534,7 +10636,7 @@
         <v>9328955.84</v>
       </c>
       <c r="H11">
-        <v>51.60873457642791</v>
+        <v>51.60873457642792</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -10850,7 +10952,7 @@
         <v>2183025.99</v>
       </c>
       <c r="D19">
-        <v>6.830336424678323</v>
+        <v>6.830336424678321</v>
       </c>
       <c r="E19">
         <v>13746834.46</v>
@@ -10979,13 +11081,13 @@
         <v>14141187.11</v>
       </c>
       <c r="F22">
-        <v>44.75489017595933</v>
+        <v>44.75489017595932</v>
       </c>
       <c r="G22">
         <v>11229376.77</v>
       </c>
       <c r="H22">
-        <v>35.53941548021982</v>
+        <v>35.53941548021981</v>
       </c>
       <c r="I22">
         <v>3978081.07</v>
@@ -11008,7 +11110,7 @@
         <v>36</v>
       </c>
       <c r="B23">
-        <v>31410809.76000001</v>
+        <v>31410809.76</v>
       </c>
       <c r="C23">
         <v>3188378.94</v>
@@ -11020,13 +11122,13 @@
         <v>12947997.82</v>
       </c>
       <c r="F23">
-        <v>41.22147094879606</v>
+        <v>41.22147094879607</v>
       </c>
       <c r="G23">
         <v>11374125.86</v>
       </c>
       <c r="H23">
-        <v>36.21086481662228</v>
+        <v>36.21086481662229</v>
       </c>
       <c r="I23">
         <v>3900307.14</v>
@@ -11055,13 +11157,13 @@
         <v>2711353.67</v>
       </c>
       <c r="D24">
-        <v>9.690951176201969</v>
+        <v>9.690951176201967</v>
       </c>
       <c r="E24">
         <v>11988382.74</v>
       </c>
       <c r="F24">
-        <v>42.84901416603551</v>
+        <v>42.84901416603552</v>
       </c>
       <c r="G24">
         <v>9675988</v>
@@ -11172,19 +11274,19 @@
         <v>40</v>
       </c>
       <c r="B27">
-        <v>38059751.67</v>
+        <v>38059751.66999999</v>
       </c>
       <c r="C27">
         <v>3474608.93</v>
       </c>
       <c r="D27">
-        <v>9.129352603576775</v>
+        <v>9.129352603576777</v>
       </c>
       <c r="E27">
         <v>16551631.31</v>
       </c>
       <c r="F27">
-        <v>43.48854257776611</v>
+        <v>43.48854257776612</v>
       </c>
       <c r="G27">
         <v>12596879.67</v>
@@ -11298,10 +11400,10 @@
         <v>36745995.5</v>
       </c>
       <c r="C30">
-        <v>2941762.529999999</v>
+        <v>2941762.53</v>
       </c>
       <c r="D30">
-        <v>8.005668345548019</v>
+        <v>8.00566834554802</v>
       </c>
       <c r="E30">
         <v>14979049.1</v>
@@ -11336,7 +11438,7 @@
         <v>44</v>
       </c>
       <c r="B31">
-        <v>37315851.98999999</v>
+        <v>37315851.99</v>
       </c>
       <c r="C31">
         <v>3146660.36</v>
@@ -11348,13 +11450,13 @@
         <v>15934601.05</v>
       </c>
       <c r="F31">
-        <v>42.70196230350093</v>
+        <v>42.70196230350092</v>
       </c>
       <c r="G31">
         <v>10935988.39</v>
       </c>
       <c r="H31">
-        <v>29.30654884398903</v>
+        <v>29.30654884398902</v>
       </c>
       <c r="I31">
         <v>7298602.189999999</v>
@@ -11465,25 +11567,25 @@
         <v>3120146.17</v>
       </c>
       <c r="D34">
-        <v>8.244016366070497</v>
+        <v>8.244016366070499</v>
       </c>
       <c r="E34">
         <v>15914219.34</v>
       </c>
       <c r="F34">
-        <v>42.04837771821299</v>
+        <v>42.048377718213</v>
       </c>
       <c r="G34">
         <v>13229250.66</v>
       </c>
       <c r="H34">
-        <v>34.95418259583938</v>
+        <v>34.95418259583939</v>
       </c>
       <c r="I34">
         <v>5583787.71</v>
       </c>
       <c r="J34">
-        <v>14.75342331987712</v>
+        <v>14.75342331987713</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -11500,13 +11602,13 @@
         <v>48</v>
       </c>
       <c r="B35">
-        <v>38166386.47</v>
+        <v>38166386.47000001</v>
       </c>
       <c r="C35">
         <v>2764793.6</v>
       </c>
       <c r="D35">
-        <v>7.244053880168133</v>
+        <v>7.244053880168131</v>
       </c>
       <c r="E35">
         <v>15903815.13</v>
@@ -11518,13 +11620,13 @@
         <v>13160501.06</v>
       </c>
       <c r="H35">
-        <v>34.48191531138159</v>
+        <v>34.48191531138158</v>
       </c>
       <c r="I35">
         <v>6337276.68</v>
       </c>
       <c r="J35">
-        <v>16.60434027460604</v>
+        <v>16.60434027460603</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -11585,10 +11687,10 @@
         <v>29802566.34</v>
       </c>
       <c r="C37">
-        <v>2344135.410000001</v>
+        <v>2344135.41</v>
       </c>
       <c r="D37">
-        <v>7.8655488364899</v>
+        <v>7.865548836489898</v>
       </c>
       <c r="E37">
         <v>12771363.46</v>
@@ -11711,7 +11813,7 @@
         <v>1548108.83</v>
       </c>
       <c r="D40">
-        <v>4.057459356337636</v>
+        <v>4.057459356337635</v>
       </c>
       <c r="E40">
         <v>17643933.6</v>
@@ -11831,10 +11933,10 @@
         <v>36723245.33</v>
       </c>
       <c r="C43">
-        <v>2184076.35</v>
+        <v>2184076.349999999</v>
       </c>
       <c r="D43">
-        <v>5.947394709736564</v>
+        <v>5.947394709736563</v>
       </c>
       <c r="E43">
         <v>18043864.47</v>
@@ -11875,7 +11977,7 @@
         <v>2420052.83</v>
       </c>
       <c r="D44">
-        <v>6.779902697302459</v>
+        <v>6.779902697302457</v>
       </c>
       <c r="E44">
         <v>15560701.81</v>
@@ -11916,13 +12018,13 @@
         <v>1188397.24</v>
       </c>
       <c r="D45">
-        <v>3.539065543987973</v>
+        <v>3.539065543987972</v>
       </c>
       <c r="E45">
         <v>17087130.04</v>
       </c>
       <c r="F45">
-        <v>50.88574016732472</v>
+        <v>50.88574016732471</v>
       </c>
       <c r="G45">
         <v>9270686.43</v>
@@ -12039,13 +12141,13 @@
         <v>1908211.71</v>
       </c>
       <c r="D48">
-        <v>5.335024600122201</v>
+        <v>5.335024600122203</v>
       </c>
       <c r="E48">
         <v>18186784.6</v>
       </c>
       <c r="F48">
-        <v>50.84705367316062</v>
+        <v>50.84705367316064</v>
       </c>
       <c r="G48">
         <v>12404111.34</v>
@@ -12057,7 +12159,7 @@
         <v>3268519.55</v>
       </c>
       <c r="J48">
-        <v>9.138206266028179</v>
+        <v>9.138206266028181</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -12118,10 +12220,10 @@
         <v>37568883.94</v>
       </c>
       <c r="C50">
-        <v>2152921.040000001</v>
+        <v>2152921.04</v>
       </c>
       <c r="D50">
-        <v>5.730596212116278</v>
+        <v>5.730596212116277</v>
       </c>
       <c r="E50">
         <v>19422696.53</v>
@@ -12162,7 +12264,7 @@
         <v>1164513.8</v>
       </c>
       <c r="D51">
-        <v>2.986829979994888</v>
+        <v>2.986829979994889</v>
       </c>
       <c r="E51">
         <v>21602522.56</v>
@@ -12238,7 +12340,7 @@
         <v>66</v>
       </c>
       <c r="B53">
-        <v>38875407.78999999</v>
+        <v>38875407.79</v>
       </c>
       <c r="C53">
         <v>1289632.45</v>
@@ -12250,25 +12352,25 @@
         <v>23679929.68</v>
       </c>
       <c r="F53">
-        <v>60.91236343530071</v>
+        <v>60.9123634353007</v>
       </c>
       <c r="G53">
         <v>8574598.35</v>
       </c>
       <c r="H53">
-        <v>22.05661326131649</v>
+        <v>22.05661326131648</v>
       </c>
       <c r="I53">
         <v>2320394.86</v>
       </c>
       <c r="J53">
-        <v>5.968798764850205</v>
+        <v>5.968798764850204</v>
       </c>
       <c r="K53">
         <v>3010852.45</v>
       </c>
       <c r="L53">
-        <v>7.744876828724838</v>
+        <v>7.744876828724837</v>
       </c>
       <c r="M53" s="2">
         <v>42296</v>
@@ -12285,7 +12387,7 @@
         <v>1195508.24</v>
       </c>
       <c r="D54">
-        <v>2.998234091916751</v>
+        <v>2.99823409191675</v>
       </c>
       <c r="E54">
         <v>24324650.16</v>
@@ -12402,7 +12504,7 @@
         <v>70</v>
       </c>
       <c r="B57">
-        <v>40609429.79</v>
+        <v>40609429.79000001</v>
       </c>
       <c r="C57">
         <v>1458857.72</v>
@@ -12414,13 +12516,13 @@
         <v>23089187.59</v>
       </c>
       <c r="F57">
-        <v>56.85671458427044</v>
+        <v>56.85671458427043</v>
       </c>
       <c r="G57">
         <v>11008413.46</v>
       </c>
       <c r="H57">
-        <v>27.10802273493336</v>
+        <v>27.10802273493335</v>
       </c>
       <c r="I57">
         <v>5052971.02</v>
@@ -12449,7 +12551,7 @@
         <v>1435684.98</v>
       </c>
       <c r="D58">
-        <v>4.288760750676785</v>
+        <v>4.288760750676786</v>
       </c>
       <c r="E58">
         <v>18932589.3</v>
@@ -12531,7 +12633,7 @@
         <v>1832790.23</v>
       </c>
       <c r="D60">
-        <v>4.409603345699185</v>
+        <v>4.409603345699186</v>
       </c>
       <c r="E60">
         <v>23484290.66</v>
@@ -12569,7 +12671,7 @@
         <v>41483031.3</v>
       </c>
       <c r="C61">
-        <v>2566375.200000001</v>
+        <v>2566375.2</v>
       </c>
       <c r="D61">
         <v>6.18656621653394</v>
@@ -12613,7 +12715,7 @@
         <v>2147386.97</v>
       </c>
       <c r="D62">
-        <v>6.363946503040678</v>
+        <v>6.363946503040675</v>
       </c>
       <c r="E62">
         <v>18641847.35</v>
@@ -12625,7 +12727,7 @@
         <v>8790872.040000001</v>
       </c>
       <c r="H62">
-        <v>26.05242564996847</v>
+        <v>26.05242564996846</v>
       </c>
       <c r="I62">
         <v>4162901.52</v>
@@ -12689,10 +12791,10 @@
         <v>77</v>
       </c>
       <c r="B64">
-        <v>39048158.30999999</v>
+        <v>39048158.31</v>
       </c>
       <c r="C64">
-        <v>2195185.24</v>
+        <v>2195185.240000001</v>
       </c>
       <c r="D64">
         <v>5.621738220206474</v>
@@ -12701,7 +12803,7 @@
         <v>21898430.54</v>
       </c>
       <c r="F64">
-        <v>56.08057201097739</v>
+        <v>56.08057201097738</v>
       </c>
       <c r="G64">
         <v>6967175.58</v>
@@ -12713,7 +12815,7 @@
         <v>7987366.95</v>
       </c>
       <c r="J64">
-        <v>20.45516945149878</v>
+        <v>20.45516945149877</v>
       </c>
       <c r="K64">
         <v>0</v>
@@ -12736,7 +12838,7 @@
         <v>1109443.87</v>
       </c>
       <c r="D65">
-        <v>3.083313129338462</v>
+        <v>3.083313129338463</v>
       </c>
       <c r="E65">
         <v>21325763.04</v>
@@ -12774,7 +12876,7 @@
         <v>27476884.45</v>
       </c>
       <c r="C66">
-        <v>429147.9399999999</v>
+        <v>429147.94</v>
       </c>
       <c r="D66">
         <v>1.561850801465229</v>
@@ -12906,25 +13008,25 @@
         <v>11672630.9</v>
       </c>
       <c r="F69">
-        <v>39.15723301311188</v>
+        <v>39.15723301311189</v>
       </c>
       <c r="G69">
         <v>8099992.000000001</v>
       </c>
       <c r="H69">
-        <v>27.17238957228932</v>
+        <v>27.17238957228933</v>
       </c>
       <c r="I69">
         <v>8698553.809999999</v>
       </c>
       <c r="J69">
-        <v>29.18033657821409</v>
+        <v>29.1803365782141</v>
       </c>
       <c r="K69">
         <v>893912.25</v>
       </c>
       <c r="L69">
-        <v>2.998735295101734</v>
+        <v>2.998735295101735</v>
       </c>
       <c r="M69" s="2">
         <v>42408</v>
@@ -12982,13 +13084,13 @@
         <v>551265.5</v>
       </c>
       <c r="D71">
-        <v>1.655305089605946</v>
+        <v>1.655305089605947</v>
       </c>
       <c r="E71">
         <v>12519091.16</v>
       </c>
       <c r="F71">
-        <v>37.59153314399107</v>
+        <v>37.59153314399108</v>
       </c>
       <c r="G71">
         <v>8791600.74</v>
@@ -13017,25 +13119,25 @@
         <v>85</v>
       </c>
       <c r="B72">
-        <v>35684645.58</v>
+        <v>35684645.58000001</v>
       </c>
       <c r="C72">
-        <v>934252.28</v>
+        <v>934252.2799999999</v>
       </c>
       <c r="D72">
-        <v>2.618079190125447</v>
+        <v>2.618079190125446</v>
       </c>
       <c r="E72">
         <v>12267330.83</v>
       </c>
       <c r="F72">
-        <v>34.37705666012109</v>
+        <v>34.37705666012108</v>
       </c>
       <c r="G72">
         <v>10161558.3</v>
       </c>
       <c r="H72">
-        <v>28.47599614579106</v>
+        <v>28.47599614579105</v>
       </c>
       <c r="I72">
         <v>11029044.59</v>
@@ -13047,7 +13149,7 @@
         <v>1292459.58</v>
       </c>
       <c r="L72">
-        <v>3.621892718823523</v>
+        <v>3.621892718823522</v>
       </c>
       <c r="M72" s="2">
         <v>42429</v>
@@ -13061,10 +13163,10 @@
         <v>36322717.23</v>
       </c>
       <c r="C73">
-        <v>878028.98</v>
+        <v>878028.9800000001</v>
       </c>
       <c r="D73">
-        <v>2.417299824900792</v>
+        <v>2.417299824900793</v>
       </c>
       <c r="E73">
         <v>13133634.89</v>
@@ -13187,7 +13289,7 @@
         <v>1795245.72</v>
       </c>
       <c r="D76">
-        <v>4.733507174269549</v>
+        <v>4.733507174269548</v>
       </c>
       <c r="E76">
         <v>13414493.87</v>
@@ -13228,7 +13330,7 @@
         <v>1698611.55</v>
       </c>
       <c r="D77">
-        <v>4.332406817732631</v>
+        <v>4.33240681773263</v>
       </c>
       <c r="E77">
         <v>14142576.6</v>
@@ -13263,13 +13365,13 @@
         <v>91</v>
       </c>
       <c r="B78">
-        <v>39529726.92999999</v>
+        <v>39529726.93</v>
       </c>
       <c r="C78">
         <v>1863359.89</v>
       </c>
       <c r="D78">
-        <v>4.713819281624875</v>
+        <v>4.713819281624873</v>
       </c>
       <c r="E78">
         <v>14282784.45</v>
@@ -13293,7 +13395,7 @@
         <v>3343569.28</v>
       </c>
       <c r="L78">
-        <v>8.458366752497071</v>
+        <v>8.458366752497069</v>
       </c>
       <c r="M78" s="2">
         <v>42471</v>
@@ -13386,7 +13488,7 @@
         <v>94</v>
       </c>
       <c r="B81">
-        <v>37047876.06999999</v>
+        <v>37047876.07</v>
       </c>
       <c r="C81">
         <v>1231480.88</v>
@@ -13398,7 +13500,7 @@
         <v>13955722.42</v>
       </c>
       <c r="F81">
-        <v>37.66942642982125</v>
+        <v>37.66942642982124</v>
       </c>
       <c r="G81">
         <v>12053491.71</v>
@@ -13416,7 +13518,7 @@
         <v>2907264.62</v>
       </c>
       <c r="L81">
-        <v>7.847317925882924</v>
+        <v>7.847317925882923</v>
       </c>
       <c r="M81" s="2">
         <v>42492</v>
@@ -13427,7 +13529,7 @@
         <v>95</v>
       </c>
       <c r="B82">
-        <v>36412675.70999999</v>
+        <v>36412675.71</v>
       </c>
       <c r="C82">
         <v>1297892.43</v>
@@ -13439,13 +13541,13 @@
         <v>12782731.38</v>
       </c>
       <c r="F82">
-        <v>35.10516909497395</v>
+        <v>35.10516909497393</v>
       </c>
       <c r="G82">
         <v>11695333.28</v>
       </c>
       <c r="H82">
-        <v>32.11885161404966</v>
+        <v>32.11885161404965</v>
       </c>
       <c r="I82">
         <v>4718284.24</v>
@@ -13597,7 +13699,7 @@
         <v>2355285.91</v>
       </c>
       <c r="D86">
-        <v>5.985988265674241</v>
+        <v>5.985988265674242</v>
       </c>
       <c r="E86">
         <v>12502068.47</v>
@@ -13638,7 +13740,7 @@
         <v>3489487.24</v>
       </c>
       <c r="D87">
-        <v>8.170354326162723</v>
+        <v>8.170354326162721</v>
       </c>
       <c r="E87">
         <v>15471446.28</v>
@@ -13662,7 +13764,7 @@
         <v>3265057.11</v>
       </c>
       <c r="L87">
-        <v>7.644869188246939</v>
+        <v>7.644869188246937</v>
       </c>
       <c r="M87" s="2">
         <v>42534</v>
@@ -13720,7 +13822,7 @@
         <v>2914704.74</v>
       </c>
       <c r="D89">
-        <v>6.831750618379365</v>
+        <v>6.831750618379363</v>
       </c>
       <c r="E89">
         <v>15837950.05</v>
@@ -13761,7 +13863,7 @@
         <v>2572122.7</v>
       </c>
       <c r="D90">
-        <v>7.26470647345858</v>
+        <v>7.264706473458579</v>
       </c>
       <c r="E90">
         <v>12455117.4</v>
@@ -13837,7 +13939,7 @@
         <v>105</v>
       </c>
       <c r="B92">
-        <v>45546248.26</v>
+        <v>45546248.25999999</v>
       </c>
       <c r="C92">
         <v>1446414.02</v>
@@ -13849,7 +13951,7 @@
         <v>20435255.87</v>
       </c>
       <c r="F92">
-        <v>44.8670453674816</v>
+        <v>44.86704536748161</v>
       </c>
       <c r="G92">
         <v>11899772.17</v>
@@ -13861,7 +13963,7 @@
         <v>11764806.2</v>
       </c>
       <c r="J92">
-        <v>25.83046167236607</v>
+        <v>25.83046167236608</v>
       </c>
       <c r="K92">
         <v>0</v>
@@ -13884,31 +13986,31 @@
         <v>2130112.86</v>
       </c>
       <c r="D93">
-        <v>4.613385573895084</v>
+        <v>4.613385573895085</v>
       </c>
       <c r="E93">
         <v>21009063.39</v>
       </c>
       <c r="F93">
-        <v>45.5013026701662</v>
+        <v>45.50130267016621</v>
       </c>
       <c r="G93">
         <v>10721188.73</v>
       </c>
       <c r="H93">
-        <v>23.21988583364947</v>
+        <v>23.21988583364948</v>
       </c>
       <c r="I93">
         <v>10859686.06</v>
       </c>
       <c r="J93">
-        <v>23.51984251493301</v>
+        <v>23.51984251493302</v>
       </c>
       <c r="K93">
         <v>1452392.73</v>
       </c>
       <c r="L93">
-        <v>3.145583407356218</v>
+        <v>3.145583407356219</v>
       </c>
       <c r="M93" s="2">
         <v>42576</v>
@@ -14042,25 +14144,25 @@
         <v>110</v>
       </c>
       <c r="B97">
-        <v>47362828.44</v>
+        <v>47362828.44000001</v>
       </c>
       <c r="C97">
         <v>1819304.83</v>
       </c>
       <c r="D97">
-        <v>3.841208158217842</v>
+        <v>3.841208158217841</v>
       </c>
       <c r="E97">
         <v>23838715.46</v>
       </c>
       <c r="F97">
-        <v>50.33211960767773</v>
+        <v>50.33211960767772</v>
       </c>
       <c r="G97">
         <v>6717052.160000002</v>
       </c>
       <c r="H97">
-        <v>14.18211787860025</v>
+        <v>14.18211787860024</v>
       </c>
       <c r="I97">
         <v>14987755.99</v>
@@ -14183,7 +14285,7 @@
         <v>9148469.539999999</v>
       </c>
       <c r="H100">
-        <v>19.35264875884013</v>
+        <v>19.35264875884014</v>
       </c>
       <c r="I100">
         <v>12859459.07</v>
@@ -14206,25 +14308,25 @@
         <v>114</v>
       </c>
       <c r="B101">
-        <v>48679038.29000001</v>
+        <v>48679038.29</v>
       </c>
       <c r="C101">
         <v>1946720.18</v>
       </c>
       <c r="D101">
-        <v>3.999093343633104</v>
+        <v>3.999093343633105</v>
       </c>
       <c r="E101">
         <v>23987288.71</v>
       </c>
       <c r="F101">
-        <v>49.27642277379921</v>
+        <v>49.27642277379922</v>
       </c>
       <c r="G101">
         <v>9565849.710000001</v>
       </c>
       <c r="H101">
-        <v>19.65086009508344</v>
+        <v>19.65086009508345</v>
       </c>
       <c r="I101">
         <v>13179179.69</v>
@@ -14247,7 +14349,7 @@
         <v>115</v>
       </c>
       <c r="B102">
-        <v>49618924.26</v>
+        <v>49618924.26000001</v>
       </c>
       <c r="C102">
         <v>1883718.47</v>
@@ -14294,7 +14396,7 @@
         <v>2405400.81</v>
       </c>
       <c r="D103">
-        <v>4.852610390241775</v>
+        <v>4.852610390241773</v>
       </c>
       <c r="E103">
         <v>23981854.86</v>
@@ -14329,19 +14431,19 @@
         <v>117</v>
       </c>
       <c r="B104">
-        <v>47060797.21999999</v>
+        <v>47060797.22</v>
       </c>
       <c r="C104">
         <v>1555963.27</v>
       </c>
       <c r="D104">
-        <v>3.306283280170919</v>
+        <v>3.306283280170917</v>
       </c>
       <c r="E104">
         <v>23436952.59</v>
       </c>
       <c r="F104">
-        <v>49.80143553547732</v>
+        <v>49.8014355354773</v>
       </c>
       <c r="G104">
         <v>9811258.180000002</v>
@@ -14417,7 +14519,7 @@
         <v>2195698.18</v>
       </c>
       <c r="D106">
-        <v>3.590796196092122</v>
+        <v>3.590796196092121</v>
       </c>
       <c r="E106">
         <v>26997310.08</v>
@@ -14441,7 +14543,7 @@
         <v>2783178.99</v>
       </c>
       <c r="L106">
-        <v>4.551549307353123</v>
+        <v>4.551549307353124</v>
       </c>
       <c r="M106" s="2">
         <v>42667</v>
@@ -14458,19 +14560,19 @@
         <v>2629553.73</v>
       </c>
       <c r="D107">
-        <v>4.437869847650752</v>
+        <v>4.437869847650753</v>
       </c>
       <c r="E107">
         <v>25595728.77</v>
       </c>
       <c r="F107">
-        <v>43.19763906745875</v>
+        <v>43.19763906745876</v>
       </c>
       <c r="G107">
         <v>13474128.61</v>
       </c>
       <c r="H107">
-        <v>22.74014346977703</v>
+        <v>22.74014346977704</v>
       </c>
       <c r="I107">
         <v>11101402.37</v>
@@ -14742,7 +14844,7 @@
         <v>62001104.47</v>
       </c>
       <c r="C114">
-        <v>3687659.04</v>
+        <v>3687659.040000001</v>
       </c>
       <c r="D114">
         <v>5.947731208214718</v>
@@ -14909,7 +15011,7 @@
         <v>2563348.92</v>
       </c>
       <c r="D118">
-        <v>4.168108657501334</v>
+        <v>4.168108657501335</v>
       </c>
       <c r="E118">
         <v>30420291.79</v>
@@ -14944,37 +15046,37 @@
         <v>132</v>
       </c>
       <c r="B119">
-        <v>77947229.14999999</v>
+        <v>77947229.15000001</v>
       </c>
       <c r="C119">
         <v>3912371.06</v>
       </c>
       <c r="D119">
-        <v>5.019256107835618</v>
+        <v>5.019256107835617</v>
       </c>
       <c r="E119">
         <v>37581931.48</v>
       </c>
       <c r="F119">
-        <v>48.21458298110653</v>
+        <v>48.21458298110652</v>
       </c>
       <c r="G119">
         <v>6578897.28</v>
       </c>
       <c r="H119">
-        <v>8.440193900080413</v>
+        <v>8.440193900080411</v>
       </c>
       <c r="I119">
         <v>10387778.32</v>
       </c>
       <c r="J119">
-        <v>13.32668067008512</v>
+        <v>13.32668067008511</v>
       </c>
       <c r="K119">
         <v>19486251.01</v>
       </c>
       <c r="L119">
-        <v>24.99928634089234</v>
+        <v>24.99928634089233</v>
       </c>
       <c r="M119" s="2">
         <v>42758</v>
@@ -14988,10 +15090,10 @@
         <v>78599132.78</v>
       </c>
       <c r="C120">
-        <v>4389349.010000001</v>
+        <v>4389349.01</v>
       </c>
       <c r="D120">
-        <v>5.584475114103162</v>
+        <v>5.584475114103161</v>
       </c>
       <c r="E120">
         <v>40571471.15</v>
@@ -15029,10 +15131,10 @@
         <v>79462405.46000001</v>
       </c>
       <c r="C121">
-        <v>4698075.74</v>
+        <v>4698075.739999999</v>
       </c>
       <c r="D121">
-        <v>5.912325096129805</v>
+        <v>5.912325096129803</v>
       </c>
       <c r="E121">
         <v>40753981.78</v>
@@ -15108,19 +15210,19 @@
         <v>136</v>
       </c>
       <c r="B123">
-        <v>64536475.54000001</v>
+        <v>64536475.53999999</v>
       </c>
       <c r="C123">
         <v>3492944.26</v>
       </c>
       <c r="D123">
-        <v>5.412356703357711</v>
+        <v>5.412356703357713</v>
       </c>
       <c r="E123">
         <v>31248348.06</v>
       </c>
       <c r="F123">
-        <v>48.4196693397552</v>
+        <v>48.41966933975522</v>
       </c>
       <c r="G123">
         <v>6729332.23</v>
@@ -15132,13 +15234,13 @@
         <v>17876640.99</v>
       </c>
       <c r="J123">
-        <v>27.70005774319048</v>
+        <v>27.70005774319049</v>
       </c>
       <c r="K123">
         <v>5189210</v>
       </c>
       <c r="L123">
-        <v>8.040739684930118</v>
+        <v>8.04073968493012</v>
       </c>
       <c r="M123" s="2">
         <v>42786</v>
@@ -15196,7 +15298,7 @@
         <v>2840003.29</v>
       </c>
       <c r="D125">
-        <v>3.268161758520058</v>
+        <v>3.268161758520057</v>
       </c>
       <c r="E125">
         <v>43118575.31999999</v>
@@ -15237,7 +15339,7 @@
         <v>2873273.02</v>
       </c>
       <c r="D126">
-        <v>3.253872832575881</v>
+        <v>3.25387283257588</v>
       </c>
       <c r="E126">
         <v>44928994.71</v>
@@ -15357,7 +15459,7 @@
         <v>89551857.94</v>
       </c>
       <c r="C129">
-        <v>3462460.69</v>
+        <v>3462460.689999999</v>
       </c>
       <c r="D129">
         <v>3.866430881110092</v>
@@ -15398,10 +15500,10 @@
         <v>76485051.19</v>
       </c>
       <c r="C130">
-        <v>4039460.16</v>
+        <v>4039460.160000001</v>
       </c>
       <c r="D130">
-        <v>5.281372107557845</v>
+        <v>5.281372107557846</v>
       </c>
       <c r="E130">
         <v>41066164.20999999</v>
@@ -15480,22 +15582,22 @@
         <v>100553248.42</v>
       </c>
       <c r="C132">
-        <v>5702264.19</v>
+        <v>5702264.189999999</v>
       </c>
       <c r="D132">
-        <v>5.670890080231185</v>
+        <v>5.670890080231183</v>
       </c>
       <c r="E132">
         <v>54946582.94999999</v>
       </c>
       <c r="F132">
-        <v>54.6442644204731</v>
+        <v>54.64426442047309</v>
       </c>
       <c r="G132">
         <v>10833670.55</v>
       </c>
       <c r="H132">
-        <v>10.7740632154905</v>
+        <v>10.77406321549049</v>
       </c>
       <c r="I132">
         <v>20075009.33</v>
@@ -15507,7 +15609,7 @@
         <v>8995721.399999999</v>
       </c>
       <c r="L132">
-        <v>8.946226543001224</v>
+        <v>8.946226543001222</v>
       </c>
       <c r="M132" s="2">
         <v>42849</v>
@@ -15521,10 +15623,10 @@
         <v>112782402.81</v>
       </c>
       <c r="C133">
-        <v>5267234.159999999</v>
+        <v>5267234.16</v>
       </c>
       <c r="D133">
-        <v>4.670262406869888</v>
+        <v>4.67026240686989</v>
       </c>
       <c r="E133">
         <v>62319133.02000001</v>
@@ -15562,10 +15664,10 @@
         <v>125130433.74</v>
       </c>
       <c r="C134">
-        <v>7124106.99</v>
+        <v>7124106.990000001</v>
       </c>
       <c r="D134">
-        <v>5.693344758000836</v>
+        <v>5.693344758000837</v>
       </c>
       <c r="E134">
         <v>66630549.28999999</v>
@@ -15603,7 +15705,7 @@
         <v>135105277.94</v>
       </c>
       <c r="C135">
-        <v>7190584.24</v>
+        <v>7190584.239999999</v>
       </c>
       <c r="D135">
         <v>5.322208243554575</v>
@@ -15647,13 +15749,13 @@
         <v>9829145.58</v>
       </c>
       <c r="D136">
-        <v>5.908213965097658</v>
+        <v>5.908213965097656</v>
       </c>
       <c r="E136">
         <v>88265519.34999999</v>
       </c>
       <c r="F136">
-        <v>53.05563640459047</v>
+        <v>53.05563640459046</v>
       </c>
       <c r="G136">
         <v>26101094.02</v>
@@ -15665,13 +15767,13 @@
         <v>36433649.2</v>
       </c>
       <c r="J136">
-        <v>21.89994982279112</v>
+        <v>21.89994982279111</v>
       </c>
       <c r="K136">
         <v>5734668</v>
       </c>
       <c r="L136">
-        <v>3.447059084335859</v>
+        <v>3.447059084335858</v>
       </c>
       <c r="M136" s="2">
         <v>42877</v>
@@ -15694,13 +15796,13 @@
         <v>88587456.46000001</v>
       </c>
       <c r="F137">
-        <v>51.67751573925421</v>
+        <v>51.67751573925422</v>
       </c>
       <c r="G137">
         <v>25498215.33</v>
       </c>
       <c r="H137">
-        <v>14.87439053670023</v>
+        <v>14.87439053670024</v>
       </c>
       <c r="I137">
         <v>31898168.47</v>
@@ -15712,7 +15814,7 @@
         <v>13753254.95</v>
       </c>
       <c r="L137">
-        <v>8.02296484791297</v>
+        <v>8.022964847912972</v>
       </c>
       <c r="M137" s="2">
         <v>42884</v>
@@ -15808,7 +15910,7 @@
         <v>271866822.45</v>
       </c>
       <c r="C140">
-        <v>18940010.83</v>
+        <v>18940010.82999999</v>
       </c>
       <c r="D140">
         <v>6.966650310367798</v>
@@ -15817,19 +15919,19 @@
         <v>134381245.12</v>
       </c>
       <c r="F140">
-        <v>49.42907115660077</v>
+        <v>49.42907115660078</v>
       </c>
       <c r="G140">
         <v>54724199.06</v>
       </c>
       <c r="H140">
-        <v>20.12904648196435</v>
+        <v>20.12904648196436</v>
       </c>
       <c r="I140">
         <v>63821367.44</v>
       </c>
       <c r="J140">
-        <v>23.47523205106706</v>
+        <v>23.47523205106707</v>
       </c>
       <c r="K140">
         <v>0</v>
@@ -15852,25 +15954,25 @@
         <v>15223665.35</v>
       </c>
       <c r="D141">
-        <v>4.941022421560984</v>
+        <v>4.941022421560982</v>
       </c>
       <c r="E141">
         <v>158632418.16</v>
       </c>
       <c r="F141">
-        <v>51.48604602734505</v>
+        <v>51.48604602734503</v>
       </c>
       <c r="G141">
         <v>79621761.52000001</v>
       </c>
       <c r="H141">
-        <v>25.84219370760811</v>
+        <v>25.8421937076081</v>
       </c>
       <c r="I141">
         <v>54629749.94</v>
       </c>
       <c r="J141">
-        <v>17.73073784348589</v>
+        <v>17.73073784348588</v>
       </c>
       <c r="K141">
         <v>0</v>
@@ -15893,7 +15995,7 @@
         <v>13257485.8</v>
       </c>
       <c r="D142">
-        <v>5.377839160691486</v>
+        <v>5.377839160691485</v>
       </c>
       <c r="E142">
         <v>126398353.77</v>
@@ -15975,7 +16077,7 @@
         <v>19480751.45</v>
       </c>
       <c r="D144">
-        <v>5.436477411016936</v>
+        <v>5.436477411016938</v>
       </c>
       <c r="E144">
         <v>190989609.04</v>
@@ -16016,7 +16118,7 @@
         <v>22098660.53</v>
       </c>
       <c r="D145">
-        <v>5.457943206104253</v>
+        <v>5.457943206104252</v>
       </c>
       <c r="E145">
         <v>214972099</v>
@@ -16051,7 +16153,7 @@
         <v>159</v>
       </c>
       <c r="B146">
-        <v>433251497.32</v>
+        <v>433251497.3200001</v>
       </c>
       <c r="C146">
         <v>22751266.82</v>
@@ -16098,7 +16200,7 @@
         <v>27526194.57</v>
       </c>
       <c r="D147">
-        <v>6.013685336339301</v>
+        <v>6.013685336339299</v>
       </c>
       <c r="E147">
         <v>231711643.95</v>
@@ -16133,13 +16235,13 @@
         <v>161</v>
       </c>
       <c r="B148">
-        <v>483617967.8099999</v>
+        <v>483617967.81</v>
       </c>
       <c r="C148">
-        <v>35309137.40000001</v>
+        <v>35309137.4</v>
       </c>
       <c r="D148">
-        <v>7.301039198335159</v>
+        <v>7.301039198335156</v>
       </c>
       <c r="E148">
         <v>241573068.63</v>
@@ -16151,13 +16253,13 @@
         <v>115286529.37</v>
       </c>
       <c r="H148">
-        <v>23.83834701015346</v>
+        <v>23.83834701015345</v>
       </c>
       <c r="I148">
         <v>44111932.89</v>
       </c>
       <c r="J148">
-        <v>9.121235319224192</v>
+        <v>9.121235319224191</v>
       </c>
       <c r="K148">
         <v>47337299.52</v>
@@ -16174,37 +16276,37 @@
         <v>162</v>
       </c>
       <c r="B149">
-        <v>498012299.2099999</v>
+        <v>498012299.21</v>
       </c>
       <c r="C149">
-        <v>40562937.73999999</v>
+        <v>40562937.74</v>
       </c>
       <c r="D149">
-        <v>8.144967062931025</v>
+        <v>8.144967062931023</v>
       </c>
       <c r="E149">
         <v>237807885.18</v>
       </c>
       <c r="F149">
-        <v>47.75140805904516</v>
+        <v>47.75140805904515</v>
       </c>
       <c r="G149">
         <v>144281827.21</v>
       </c>
       <c r="H149">
-        <v>28.97153894369179</v>
+        <v>28.97153894369178</v>
       </c>
       <c r="I149">
         <v>29405335.58</v>
       </c>
       <c r="J149">
-        <v>5.904540033779462</v>
+        <v>5.90454003377946</v>
       </c>
       <c r="K149">
         <v>45954313.5</v>
       </c>
       <c r="L149">
-        <v>9.227545900552581</v>
+        <v>9.227545900552579</v>
       </c>
       <c r="M149" s="2">
         <v>42968</v>
@@ -16300,10 +16402,10 @@
         <v>664216538.0899999</v>
       </c>
       <c r="C152">
-        <v>31340447.29000001</v>
+        <v>31340447.29</v>
       </c>
       <c r="D152">
-        <v>4.718408153479828</v>
+        <v>4.718408153479827</v>
       </c>
       <c r="E152">
         <v>330018644.19</v>
@@ -16338,31 +16440,31 @@
         <v>166</v>
       </c>
       <c r="B153">
-        <v>730548491.9200001</v>
+        <v>730548491.9199998</v>
       </c>
       <c r="C153">
         <v>22303513.72</v>
       </c>
       <c r="D153">
-        <v>3.052981967204222</v>
+        <v>3.052981967204223</v>
       </c>
       <c r="E153">
         <v>379848969.67</v>
       </c>
       <c r="F153">
-        <v>51.99503850479456</v>
+        <v>51.99503850479458</v>
       </c>
       <c r="G153">
         <v>246972038.14</v>
       </c>
       <c r="H153">
-        <v>33.80638532165297</v>
+        <v>33.80638532165298</v>
       </c>
       <c r="I153">
         <v>81423970.39</v>
       </c>
       <c r="J153">
-        <v>11.14559420634824</v>
+        <v>11.14559420634825</v>
       </c>
       <c r="K153">
         <v>0</v>
@@ -16385,7 +16487,7 @@
         <v>24853913.22</v>
       </c>
       <c r="D154">
-        <v>3.223043230999435</v>
+        <v>3.223043230999436</v>
       </c>
       <c r="E154">
         <v>404832940.45</v>
@@ -16464,10 +16566,10 @@
         <v>882602758</v>
       </c>
       <c r="C156">
-        <v>37274043.85</v>
+        <v>37274043.84999999</v>
       </c>
       <c r="D156">
-        <v>4.22319594088556</v>
+        <v>4.223195940885558</v>
       </c>
       <c r="E156">
         <v>516947890.61</v>
@@ -16502,10 +16604,10 @@
         <v>170</v>
       </c>
       <c r="B157">
-        <v>916908261.91</v>
+        <v>916908261.9100001</v>
       </c>
       <c r="C157">
-        <v>39510554.83</v>
+        <v>39510554.83000001</v>
       </c>
       <c r="D157">
         <v>4.30910664363478</v>
@@ -16514,13 +16616,13 @@
         <v>510064704.11</v>
       </c>
       <c r="F157">
-        <v>55.62876083671563</v>
+        <v>55.62876083671562</v>
       </c>
       <c r="G157">
         <v>312290886.3199999</v>
       </c>
       <c r="H157">
-        <v>34.05912012064007</v>
+        <v>34.05912012064006</v>
       </c>
       <c r="I157">
         <v>55042116.65000001</v>
@@ -16590,13 +16692,13 @@
         <v>49544030.16</v>
       </c>
       <c r="D159">
-        <v>4.916465571759936</v>
+        <v>4.916465571759937</v>
       </c>
       <c r="E159">
         <v>564829152.53</v>
       </c>
       <c r="F159">
-        <v>56.05040755408919</v>
+        <v>56.0504075540892</v>
       </c>
       <c r="G159">
         <v>291004003.33</v>
@@ -16608,7 +16710,7 @@
         <v>102339219.94</v>
       </c>
       <c r="J159">
-        <v>10.15555758889393</v>
+        <v>10.15555758889394</v>
       </c>
       <c r="K159">
         <v>0</v>
@@ -16628,10 +16730,10 @@
         <v>1039148079.9</v>
       </c>
       <c r="C160">
-        <v>50192445.1</v>
+        <v>50192445.09999999</v>
       </c>
       <c r="D160">
-        <v>4.830153283334764</v>
+        <v>4.830153283334763</v>
       </c>
       <c r="E160">
         <v>571431607.27</v>
@@ -16713,7 +16815,7 @@
         <v>18206845.18</v>
       </c>
       <c r="D162">
-        <v>2.655260445631043</v>
+        <v>2.655260445631044</v>
       </c>
       <c r="E162">
         <v>398049892.44</v>
@@ -16795,7 +16897,7 @@
         <v>114642144.85</v>
       </c>
       <c r="D164">
-        <v>7.93990717194277</v>
+        <v>7.939907171942768</v>
       </c>
       <c r="E164">
         <v>742372628.21</v>
@@ -16959,7 +17061,7 @@
         <v>114904003.69</v>
       </c>
       <c r="D168">
-        <v>6.991452277060812</v>
+        <v>6.991452277060811</v>
       </c>
       <c r="E168">
         <v>819616933.73</v>
@@ -17038,10 +17140,10 @@
         <v>1848761143.19</v>
       </c>
       <c r="C170">
-        <v>68561265.62</v>
+        <v>68561265.61999999</v>
       </c>
       <c r="D170">
-        <v>3.708497762003962</v>
+        <v>3.708497762003961</v>
       </c>
       <c r="E170">
         <v>1067543024.03</v>
@@ -17164,7 +17266,7 @@
         <v>203060130.12</v>
       </c>
       <c r="D173">
-        <v>7.778409161558586</v>
+        <v>7.778409161558588</v>
       </c>
       <c r="E173">
         <v>1372374378.39</v>
@@ -17205,7 +17307,7 @@
         <v>203407164.16</v>
       </c>
       <c r="D174">
-        <v>7.481749561149012</v>
+        <v>7.481749561149013</v>
       </c>
       <c r="E174">
         <v>1371955868.02</v>
@@ -17246,7 +17348,7 @@
         <v>163942211.28</v>
       </c>
       <c r="D175">
-        <v>6.854141368583172</v>
+        <v>6.85414136858317</v>
       </c>
       <c r="E175">
         <v>1127396440.56</v>
@@ -17287,7 +17389,7 @@
         <v>240162936.84</v>
       </c>
       <c r="D176">
-        <v>7.54890204656768</v>
+        <v>7.548902046567682</v>
       </c>
       <c r="E176">
         <v>1443182962.54</v>
@@ -17305,7 +17407,7 @@
         <v>509492868.0000001</v>
       </c>
       <c r="J176">
-        <v>16.01459327805927</v>
+        <v>16.01459327805928</v>
       </c>
       <c r="K176">
         <v>0</v>
@@ -17325,10 +17427,10 @@
         <v>3464142585.12</v>
       </c>
       <c r="C177">
-        <v>369929336.8199999</v>
+        <v>369929336.8200001</v>
       </c>
       <c r="D177">
-        <v>10.67881381121572</v>
+        <v>10.67881381121573</v>
       </c>
       <c r="E177">
         <v>1384140827.64</v>
@@ -17410,7 +17512,7 @@
         <v>281469017.8699999</v>
       </c>
       <c r="D179">
-        <v>7.561465593836086</v>
+        <v>7.561465593836085</v>
       </c>
       <c r="E179">
         <v>1601408721.96</v>
@@ -17457,7 +17559,7 @@
         <v>1324838750.69</v>
       </c>
       <c r="F180">
-        <v>47.0221123303153</v>
+        <v>47.02211233031531</v>
       </c>
       <c r="G180">
         <v>776201563.14</v>
@@ -17574,7 +17676,7 @@
         <v>184430173.55</v>
       </c>
       <c r="D183">
-        <v>4.982574801512583</v>
+        <v>4.982574801512584</v>
       </c>
       <c r="E183">
         <v>1407343853.77</v>
@@ -17615,7 +17717,7 @@
         <v>182720109.56</v>
       </c>
       <c r="D184">
-        <v>5.089022565628262</v>
+        <v>5.089022565628263</v>
       </c>
       <c r="E184">
         <v>1341224531.92</v>
@@ -17656,7 +17758,7 @@
         <v>137095914.73</v>
       </c>
       <c r="D185">
-        <v>3.82372911906926</v>
+        <v>3.823729119069259</v>
       </c>
       <c r="E185">
         <v>1329889166.39</v>
@@ -17703,7 +17805,7 @@
         <v>1482476670.09</v>
       </c>
       <c r="F186">
-        <v>38.60963320141006</v>
+        <v>38.60963320141007</v>
       </c>
       <c r="G186">
         <v>1344332992.9</v>
@@ -17715,7 +17817,7 @@
         <v>305836874.06</v>
       </c>
       <c r="J186">
-        <v>7.965217777225172</v>
+        <v>7.965217777225174</v>
       </c>
       <c r="K186">
         <v>536157667.34</v>
@@ -17732,25 +17834,25 @@
         <v>200</v>
       </c>
       <c r="B187">
-        <v>4011882245.419999</v>
+        <v>4011882245.42</v>
       </c>
       <c r="C187">
         <v>166667074.35</v>
       </c>
       <c r="D187">
-        <v>4.154336148332086</v>
+        <v>4.154336148332085</v>
       </c>
       <c r="E187">
         <v>1537301104.28</v>
       </c>
       <c r="F187">
-        <v>38.31869955891644</v>
+        <v>38.31869955891642</v>
       </c>
       <c r="G187">
         <v>1433134720.15</v>
       </c>
       <c r="H187">
-        <v>35.72225285989088</v>
+        <v>35.72225285989087</v>
       </c>
       <c r="I187">
         <v>813864564.0199999</v>
@@ -17762,7 +17864,7 @@
         <v>60914782.62</v>
       </c>
       <c r="L187">
-        <v>1.518359186377937</v>
+        <v>1.518359186377936</v>
       </c>
       <c r="M187" s="2">
         <v>43234</v>
@@ -17785,13 +17887,13 @@
         <v>1534725445.45</v>
       </c>
       <c r="F188">
-        <v>36.84669863504922</v>
+        <v>36.84669863504923</v>
       </c>
       <c r="G188">
         <v>1568322141.96</v>
       </c>
       <c r="H188">
-        <v>37.65331023786538</v>
+        <v>37.65331023786539</v>
       </c>
       <c r="I188">
         <v>831792963.9200001</v>
@@ -17832,7 +17934,7 @@
         <v>1307097561.56</v>
       </c>
       <c r="H189">
-        <v>37.53077464812324</v>
+        <v>37.53077464812323</v>
       </c>
       <c r="I189">
         <v>786541949.2499999</v>
@@ -17855,31 +17957,31 @@
         <v>203</v>
       </c>
       <c r="B190">
-        <v>4725151389.78</v>
+        <v>4725151389.780001</v>
       </c>
       <c r="C190">
-        <v>279195601.2900001</v>
+        <v>279195601.29</v>
       </c>
       <c r="D190">
-        <v>5.908712298485726</v>
+        <v>5.908712298485725</v>
       </c>
       <c r="E190">
         <v>1631990228.51</v>
       </c>
       <c r="F190">
-        <v>34.53836912061318</v>
+        <v>34.53836912061317</v>
       </c>
       <c r="G190">
         <v>1564193134.89</v>
       </c>
       <c r="H190">
-        <v>33.10355596803065</v>
+        <v>33.10355596803064</v>
       </c>
       <c r="I190">
         <v>1032327787.69</v>
       </c>
       <c r="J190">
-        <v>21.84750714914268</v>
+        <v>21.84750714914267</v>
       </c>
       <c r="K190">
         <v>217444637.4</v>
@@ -17937,19 +18039,19 @@
         <v>205</v>
       </c>
       <c r="B192">
-        <v>5407757370.549999</v>
+        <v>5407757370.55</v>
       </c>
       <c r="C192">
         <v>363246398.78</v>
       </c>
       <c r="D192">
-        <v>6.717135660675098</v>
+        <v>6.717135660675097</v>
       </c>
       <c r="E192">
         <v>1869031449.95</v>
       </c>
       <c r="F192">
-        <v>34.56204341061088</v>
+        <v>34.56204341061087</v>
       </c>
       <c r="G192">
         <v>1715164223.85</v>
@@ -17967,7 +18069,7 @@
         <v>339524123.57</v>
       </c>
       <c r="L192">
-        <v>6.278464441082505</v>
+        <v>6.278464441082504</v>
       </c>
       <c r="M192" s="2">
         <v>43269</v>
@@ -18019,25 +18121,25 @@
         <v>207</v>
       </c>
       <c r="B194">
-        <v>4406102418.559999</v>
+        <v>4406102418.56</v>
       </c>
       <c r="C194">
         <v>185813919.14</v>
       </c>
       <c r="D194">
-        <v>4.21719473331552</v>
+        <v>4.217194733315518</v>
       </c>
       <c r="E194">
         <v>1623823144.3</v>
       </c>
       <c r="F194">
-        <v>36.85395821622089</v>
+        <v>36.85395821622087</v>
       </c>
       <c r="G194">
         <v>1595159147.07</v>
       </c>
       <c r="H194">
-        <v>36.20340599325717</v>
+        <v>36.20340599325716</v>
       </c>
       <c r="I194">
         <v>831529598.6999999</v>
@@ -18049,7 +18151,7 @@
         <v>169776609.35</v>
       </c>
       <c r="L194">
-        <v>3.853215227926689</v>
+        <v>3.853215227926688</v>
       </c>
       <c r="M194" s="2">
         <v>43283</v>
@@ -18060,7 +18162,7 @@
         <v>208</v>
       </c>
       <c r="B195">
-        <v>5870359541.54</v>
+        <v>5870359541.540001</v>
       </c>
       <c r="C195">
         <v>176096176.78</v>
@@ -18072,25 +18174,25 @@
         <v>2408862837.02</v>
       </c>
       <c r="F195">
-        <v>41.03433222402032</v>
+        <v>41.03433222402031</v>
       </c>
       <c r="G195">
         <v>2007983145.81</v>
       </c>
       <c r="H195">
-        <v>34.20545422475496</v>
+        <v>34.20545422475495</v>
       </c>
       <c r="I195">
         <v>821803057.01</v>
       </c>
       <c r="J195">
-        <v>13.99919461822968</v>
+        <v>13.99919461822967</v>
       </c>
       <c r="K195">
         <v>455614324.92</v>
       </c>
       <c r="L195">
-        <v>7.761267801332599</v>
+        <v>7.761267801332597</v>
       </c>
       <c r="M195" s="2">
         <v>43290</v>
@@ -18101,19 +18203,19 @@
         <v>209</v>
       </c>
       <c r="B196">
-        <v>6036635086.800001</v>
+        <v>6036635086.8</v>
       </c>
       <c r="C196">
         <v>162191895.4</v>
       </c>
       <c r="D196">
-        <v>2.686793106885931</v>
+        <v>2.686793106885932</v>
       </c>
       <c r="E196">
         <v>2627281170.28</v>
       </c>
       <c r="F196">
-        <v>43.52227909261801</v>
+        <v>43.52227909261802</v>
       </c>
       <c r="G196">
         <v>1944346401.88</v>
@@ -18131,7 +18233,7 @@
         <v>466801767.07</v>
       </c>
       <c r="L196">
-        <v>7.732814065417526</v>
+        <v>7.732814065417528</v>
       </c>
       <c r="M196" s="2">
         <v>43297</v>
@@ -18189,7 +18291,7 @@
         <v>172108819.53</v>
       </c>
       <c r="D198">
-        <v>2.919045847879464</v>
+        <v>2.919045847879465</v>
       </c>
       <c r="E198">
         <v>2846194675.66</v>
@@ -18227,10 +18329,10 @@
         <v>6218599824.93</v>
       </c>
       <c r="C199">
-        <v>302028307.4899999</v>
+        <v>302028307.4900001</v>
       </c>
       <c r="D199">
-        <v>4.856853889828805</v>
+        <v>4.856853889828806</v>
       </c>
       <c r="E199">
         <v>2841151666.42</v>
@@ -18271,7 +18373,7 @@
         <v>320119074.1</v>
       </c>
       <c r="D200">
-        <v>5.071258245905268</v>
+        <v>5.071258245905269</v>
       </c>
       <c r="E200">
         <v>2456315478.62</v>
@@ -18312,7 +18414,7 @@
         <v>347575005.78</v>
       </c>
       <c r="D201">
-        <v>5.363390541863582</v>
+        <v>5.363390541863583</v>
       </c>
       <c r="E201">
         <v>2292967441.12</v>
@@ -18347,19 +18449,19 @@
         <v>215</v>
       </c>
       <c r="B202">
-        <v>6931703136.88</v>
+        <v>6931703136.880001</v>
       </c>
       <c r="C202">
-        <v>458032170.76</v>
+        <v>458032170.7599999</v>
       </c>
       <c r="D202">
-        <v>6.607786884626495</v>
+        <v>6.607786884626493</v>
       </c>
       <c r="E202">
         <v>2526690456.34</v>
       </c>
       <c r="F202">
-        <v>36.45122138737867</v>
+        <v>36.45122138737866</v>
       </c>
       <c r="G202">
         <v>1998465726.72</v>
@@ -18470,13 +18572,13 @@
         <v>218</v>
       </c>
       <c r="B205">
-        <v>7006618913.3</v>
+        <v>7006618913.299999</v>
       </c>
       <c r="C205">
         <v>341103302.71</v>
       </c>
       <c r="D205">
-        <v>4.868301058339508</v>
+        <v>4.868301058339507</v>
       </c>
       <c r="E205">
         <v>2520174099.88</v>
@@ -18494,7 +18596,7 @@
         <v>1327726349.25</v>
       </c>
       <c r="J205">
-        <v>18.94960130812456</v>
+        <v>18.94960130812457</v>
       </c>
       <c r="K205">
         <v>777849449.77</v>
@@ -18599,7 +18701,7 @@
         <v>267623213.24</v>
       </c>
       <c r="D208">
-        <v>4.31174716177746</v>
+        <v>4.311747161777461</v>
       </c>
       <c r="E208">
         <v>2211777596.9</v>
@@ -18634,19 +18736,19 @@
         <v>222</v>
       </c>
       <c r="B209">
-        <v>6305722991.559999</v>
+        <v>6305722991.560001</v>
       </c>
       <c r="C209">
         <v>263582673.18</v>
       </c>
       <c r="D209">
-        <v>4.180054746026691</v>
+        <v>4.18005474602669</v>
       </c>
       <c r="E209">
         <v>2186111056.13</v>
       </c>
       <c r="F209">
-        <v>34.66868206954281</v>
+        <v>34.6686820695428</v>
       </c>
       <c r="G209">
         <v>2046035154.83</v>
@@ -18658,13 +18760,13 @@
         <v>1159646813.87</v>
       </c>
       <c r="J209">
-        <v>18.39038624789178</v>
+        <v>18.39038624789177</v>
       </c>
       <c r="K209">
         <v>650347293.55</v>
       </c>
       <c r="L209">
-        <v>10.31360391854302</v>
+        <v>10.31360391854301</v>
       </c>
       <c r="M209" s="2">
         <v>43388</v>
@@ -18675,13 +18777,13 @@
         <v>223</v>
       </c>
       <c r="B210">
-        <v>6111298355.34</v>
+        <v>6111298355.339999</v>
       </c>
       <c r="C210">
         <v>245801588.73</v>
       </c>
       <c r="D210">
-        <v>4.022084579052185</v>
+        <v>4.022084579052187</v>
       </c>
       <c r="E210">
         <v>2051130909.75</v>
@@ -18722,7 +18824,7 @@
         <v>224220648.08</v>
       </c>
       <c r="D211">
-        <v>3.522412410511533</v>
+        <v>3.522412410511532</v>
       </c>
       <c r="E211">
         <v>2091021232.26</v>
@@ -18798,7 +18900,7 @@
         <v>226</v>
       </c>
       <c r="B213">
-        <v>6542979878.75</v>
+        <v>6542979878.749999</v>
       </c>
       <c r="C213">
         <v>224695850.1</v>
@@ -18828,7 +18930,7 @@
         <v>642077581.41</v>
       </c>
       <c r="L213">
-        <v>9.81322873229843</v>
+        <v>9.813228732298432</v>
       </c>
       <c r="M213" s="2">
         <v>43416</v>
@@ -18880,25 +18982,25 @@
         <v>228</v>
       </c>
       <c r="B215">
-        <v>6579430062.900001</v>
+        <v>6579430062.9</v>
       </c>
       <c r="C215">
         <v>227895866.51</v>
       </c>
       <c r="D215">
-        <v>3.46376303617932</v>
+        <v>3.463763036179321</v>
       </c>
       <c r="E215">
         <v>1828466835.45</v>
       </c>
       <c r="F215">
-        <v>27.79065691054812</v>
+        <v>27.79065691054813</v>
       </c>
       <c r="G215">
         <v>3077171932.31</v>
       </c>
       <c r="H215">
-        <v>46.76958190742865</v>
+        <v>46.76958190742866</v>
       </c>
       <c r="I215">
         <v>910256940.0699999</v>
@@ -18910,7 +19012,7 @@
         <v>535638488.56</v>
       </c>
       <c r="L215">
-        <v>8.141107716614405</v>
+        <v>8.141107716614407</v>
       </c>
       <c r="M215" s="2">
         <v>43430</v>
@@ -18921,13 +19023,13 @@
         <v>229</v>
       </c>
       <c r="B216">
-        <v>5302726370.809999</v>
+        <v>5302726370.81</v>
       </c>
       <c r="C216">
         <v>213882796.54</v>
       </c>
       <c r="D216">
-        <v>4.033449617867593</v>
+        <v>4.033449617867591</v>
       </c>
       <c r="E216">
         <v>1311264309.28</v>
@@ -18939,7 +19041,7 @@
         <v>2681199686.85</v>
       </c>
       <c r="H216">
-        <v>50.56266341799648</v>
+        <v>50.56266341799647</v>
       </c>
       <c r="I216">
         <v>671188949.6799999</v>
@@ -18951,7 +19053,7 @@
         <v>425190628.46</v>
       </c>
       <c r="L216">
-        <v>8.018339976970216</v>
+        <v>8.018339976970214</v>
       </c>
       <c r="M216" s="2">
         <v>43437</v>
@@ -19003,7 +19105,7 @@
         <v>231</v>
       </c>
       <c r="B218">
-        <v>5856692189.690001</v>
+        <v>5856692189.69</v>
       </c>
       <c r="C218">
         <v>251212640.19</v>
@@ -19015,7 +19117,7 @@
         <v>1269723269.94</v>
       </c>
       <c r="F218">
-        <v>21.67987028881583</v>
+        <v>21.67987028881584</v>
       </c>
       <c r="G218">
         <v>2824627709.92</v>
@@ -19044,19 +19146,19 @@
         <v>232</v>
       </c>
       <c r="B219">
-        <v>4359492458.43</v>
+        <v>4359492458.429999</v>
       </c>
       <c r="C219">
         <v>219497246.87</v>
       </c>
       <c r="D219">
-        <v>5.034926633387235</v>
+        <v>5.034926633387236</v>
       </c>
       <c r="E219">
         <v>987562565.7099999</v>
       </c>
       <c r="F219">
-        <v>22.65315458455121</v>
+        <v>22.65315458455122</v>
       </c>
       <c r="G219">
         <v>2246036006.88</v>
@@ -19074,7 +19176,7 @@
         <v>334378628</v>
       </c>
       <c r="L219">
-        <v>7.670127456085128</v>
+        <v>7.67012745608513</v>
       </c>
       <c r="M219" s="2">
         <v>43458</v>
@@ -19091,7 +19193,7 @@
         <v>186660761.17</v>
       </c>
       <c r="D220">
-        <v>4.228347073727912</v>
+        <v>4.22834707372791</v>
       </c>
       <c r="E220">
         <v>998612573.4599999</v>
@@ -19126,19 +19228,19 @@
         <v>234</v>
       </c>
       <c r="B221">
-        <v>6159042437.8</v>
+        <v>6159042437.799999</v>
       </c>
       <c r="C221">
         <v>233627840.21</v>
       </c>
       <c r="D221">
-        <v>3.793249398253075</v>
+        <v>3.793249398253076</v>
       </c>
       <c r="E221">
         <v>1542052149.57</v>
       </c>
       <c r="F221">
-        <v>25.03720611025402</v>
+        <v>25.03720611025403</v>
       </c>
       <c r="G221">
         <v>2769697927.85</v>
@@ -19150,13 +19252,13 @@
         <v>1121481962.76</v>
       </c>
       <c r="J221">
-        <v>18.20870653329337</v>
+        <v>18.20870653329338</v>
       </c>
       <c r="K221">
         <v>492182557.41</v>
       </c>
       <c r="L221">
-        <v>7.991218803580883</v>
+        <v>7.991218803580884</v>
       </c>
       <c r="M221" s="2">
         <v>43472</v>
@@ -19173,7 +19275,7 @@
         <v>243697664.87</v>
       </c>
       <c r="D222">
-        <v>3.734937694805333</v>
+        <v>3.734937694805334</v>
       </c>
       <c r="E222">
         <v>1641036426.15</v>
@@ -19331,7 +19433,7 @@
         <v>239</v>
       </c>
       <c r="B226">
-        <v>7133901305.01</v>
+        <v>7133901305.009999</v>
       </c>
       <c r="C226">
         <v>261796934.41</v>
@@ -19349,7 +19451,7 @@
         <v>2901932985.710001</v>
       </c>
       <c r="H226">
-        <v>40.67806466108564</v>
+        <v>40.67806466108565</v>
       </c>
       <c r="I226">
         <v>1163994996.12</v>
@@ -19413,7 +19515,7 @@
         <v>241</v>
       </c>
       <c r="B228">
-        <v>7571701670.22</v>
+        <v>7571701670.220001</v>
       </c>
       <c r="C228">
         <v>414352727.73</v>
@@ -19431,19 +19533,19 @@
         <v>2772881979.72</v>
       </c>
       <c r="H228">
-        <v>36.6216486133616</v>
+        <v>36.62164861336159</v>
       </c>
       <c r="I228">
         <v>1703825027.61</v>
       </c>
       <c r="J228">
-        <v>22.50253776256473</v>
+        <v>22.50253776256472</v>
       </c>
       <c r="K228">
         <v>737986371.39</v>
       </c>
       <c r="L228">
-        <v>9.746638252964308</v>
+        <v>9.746638252964306</v>
       </c>
       <c r="M228" s="2">
         <v>43521</v>
@@ -19454,7 +19556,7 @@
         <v>242</v>
       </c>
       <c r="B229">
-        <v>7457558702.969999</v>
+        <v>7457558702.970001</v>
       </c>
       <c r="C229">
         <v>385932435.02</v>
@@ -19466,25 +19568,25 @@
         <v>1940233218.04</v>
       </c>
       <c r="F229">
-        <v>26.01700228343218</v>
+        <v>26.01700228343217</v>
       </c>
       <c r="G229">
         <v>2603376323.29</v>
       </c>
       <c r="H229">
-        <v>34.90923004405177</v>
+        <v>34.90923004405175</v>
       </c>
       <c r="I229">
         <v>1910661561.86</v>
       </c>
       <c r="J229">
-        <v>25.62046961962327</v>
+        <v>25.62046961962326</v>
       </c>
       <c r="K229">
         <v>617355164.76</v>
       </c>
       <c r="L229">
-        <v>8.278247471443116</v>
+        <v>8.278247471443114</v>
       </c>
       <c r="M229" s="2">
         <v>43528</v>
@@ -19495,13 +19597,13 @@
         <v>243</v>
       </c>
       <c r="B230">
-        <v>7770528337.940001</v>
+        <v>7770528337.94</v>
       </c>
       <c r="C230">
         <v>345847916.28</v>
       </c>
       <c r="D230">
-        <v>4.450764494241401</v>
+        <v>4.450764494241402</v>
       </c>
       <c r="E230">
         <v>2168095126.79</v>
@@ -19513,7 +19615,7 @@
         <v>2648765314.55</v>
       </c>
       <c r="H230">
-        <v>34.08732584652279</v>
+        <v>34.0873258465228</v>
       </c>
       <c r="I230">
         <v>1832439026.68</v>
@@ -19525,7 +19627,7 @@
         <v>775380953.6400001</v>
       </c>
       <c r="L230">
-        <v>9.97848434390443</v>
+        <v>9.978484343904432</v>
       </c>
       <c r="M230" s="2">
         <v>43535</v>
@@ -19577,7 +19679,7 @@
         <v>245</v>
       </c>
       <c r="B232">
-        <v>7940528731.799999</v>
+        <v>7940528731.8</v>
       </c>
       <c r="C232">
         <v>344603228.28</v>
@@ -19601,7 +19703,7 @@
         <v>1916592604.3</v>
       </c>
       <c r="J232">
-        <v>24.13683860401494</v>
+        <v>24.13683860401493</v>
       </c>
       <c r="K232">
         <v>795696394.3399999</v>
@@ -19659,25 +19761,25 @@
         <v>247</v>
       </c>
       <c r="B234">
-        <v>8559763488.629999</v>
+        <v>8559763488.630001</v>
       </c>
       <c r="C234">
         <v>417230071.09</v>
       </c>
       <c r="D234">
-        <v>4.874317750066458</v>
+        <v>4.874317750066457</v>
       </c>
       <c r="E234">
         <v>2441442800.900001</v>
       </c>
       <c r="F234">
-        <v>28.52231611472663</v>
+        <v>28.52231611472662</v>
       </c>
       <c r="G234">
         <v>2598259997.35</v>
       </c>
       <c r="H234">
-        <v>30.35434332737451</v>
+        <v>30.3543433273745</v>
       </c>
       <c r="I234">
         <v>2340391525.1</v>
@@ -19689,7 +19791,7 @@
         <v>762439094.1900001</v>
       </c>
       <c r="L234">
-        <v>8.907244869589608</v>
+        <v>8.907244869589606</v>
       </c>
       <c r="M234" s="2">
         <v>43563</v>
@@ -19703,10 +19805,10 @@
         <v>6687022334.9</v>
       </c>
       <c r="C235">
-        <v>291194546.91</v>
+        <v>291194546.9100001</v>
       </c>
       <c r="D235">
-        <v>4.354622017489563</v>
+        <v>4.354622017489564</v>
       </c>
       <c r="E235">
         <v>1973777645.61</v>
@@ -19829,7 +19931,7 @@
         <v>413243637.7</v>
       </c>
       <c r="D238">
-        <v>4.913363842246953</v>
+        <v>4.913363842246954</v>
       </c>
       <c r="E238">
         <v>2243938591.83</v>
@@ -19888,7 +19990,7 @@
         <v>1958270490.43</v>
       </c>
       <c r="J239">
-        <v>24.43496021529662</v>
+        <v>24.43496021529661</v>
       </c>
       <c r="K239">
         <v>813744043.58</v>
@@ -19905,13 +20007,13 @@
         <v>253</v>
       </c>
       <c r="B240">
-        <v>7763561557.8</v>
+        <v>7763561557.799999</v>
       </c>
       <c r="C240">
         <v>218410682.79</v>
       </c>
       <c r="D240">
-        <v>2.813279461545123</v>
+        <v>2.813279461545124</v>
       </c>
       <c r="E240">
         <v>2303642799.61</v>
@@ -19935,7 +20037,7 @@
         <v>762751015.66</v>
       </c>
       <c r="L240">
-        <v>9.824756459793495</v>
+        <v>9.824756459793496</v>
       </c>
       <c r="M240" s="2">
         <v>43605</v>
@@ -19987,7 +20089,7 @@
         <v>255</v>
       </c>
       <c r="B242">
-        <v>7582362270.59</v>
+        <v>7582362270.589999</v>
       </c>
       <c r="C242">
         <v>289218098.15</v>
@@ -20028,19 +20130,19 @@
         <v>256</v>
       </c>
       <c r="B243">
-        <v>7767527760.03</v>
+        <v>7767527760.030001</v>
       </c>
       <c r="C243">
         <v>303633438.24</v>
       </c>
       <c r="D243">
-        <v>3.90901001734981</v>
+        <v>3.909010017349809</v>
       </c>
       <c r="E243">
         <v>2043067029.89</v>
       </c>
       <c r="F243">
-        <v>26.30266788878666</v>
+        <v>26.30266788878665</v>
       </c>
       <c r="G243">
         <v>2502904257.66</v>
@@ -20052,7 +20154,7 @@
         <v>2070834931.56</v>
       </c>
       <c r="J243">
-        <v>26.66015488500813</v>
+        <v>26.66015488500812</v>
       </c>
       <c r="K243">
         <v>847088102.6799999</v>
@@ -20072,10 +20174,10 @@
         <v>8096481661.049999</v>
       </c>
       <c r="C244">
-        <v>354374139.58</v>
+        <v>354374139.5799999</v>
       </c>
       <c r="D244">
-        <v>4.376890536105318</v>
+        <v>4.376890536105316</v>
       </c>
       <c r="E244">
         <v>2321576148.44</v>
@@ -20154,10 +20256,10 @@
         <v>6884049511.36</v>
       </c>
       <c r="C246">
-        <v>320857508.7600001</v>
+        <v>320857508.76</v>
       </c>
       <c r="D246">
-        <v>4.660883223319701</v>
+        <v>4.6608832233197</v>
       </c>
       <c r="E246">
         <v>2098720489.75</v>
@@ -20236,10 +20338,10 @@
         <v>8680478226.879999</v>
       </c>
       <c r="C248">
-        <v>541425475.3400002</v>
+        <v>541425475.34</v>
       </c>
       <c r="D248">
-        <v>6.237277039223716</v>
+        <v>6.237277039223715</v>
       </c>
       <c r="E248">
         <v>2417025324.12</v>
@@ -20274,19 +20376,19 @@
         <v>262</v>
       </c>
       <c r="B249">
-        <v>8764528316.689999</v>
+        <v>8764528316.690001</v>
       </c>
       <c r="C249">
-        <v>609113138.5600001</v>
+        <v>609113138.5599998</v>
       </c>
       <c r="D249">
-        <v>6.949753786522502</v>
+        <v>6.949753786522497</v>
       </c>
       <c r="E249">
         <v>2391418418.29</v>
       </c>
       <c r="F249">
-        <v>27.28519244710639</v>
+        <v>27.28519244710638</v>
       </c>
       <c r="G249">
         <v>2468552202.64</v>
@@ -20304,7 +20406,7 @@
         <v>1661163706.99</v>
       </c>
       <c r="L249">
-        <v>18.95325848655999</v>
+        <v>18.95325848655998</v>
       </c>
       <c r="M249" s="2">
         <v>43668</v>
@@ -20315,7 +20417,7 @@
         <v>263</v>
       </c>
       <c r="B250">
-        <v>8621684568.060001</v>
+        <v>8621684568.059999</v>
       </c>
       <c r="C250">
         <v>551917527.21</v>
@@ -20327,25 +20429,25 @@
         <v>2559803649.06</v>
       </c>
       <c r="F250">
-        <v>29.69029577517925</v>
+        <v>29.69029577517926</v>
       </c>
       <c r="G250">
         <v>1967718559.17</v>
       </c>
       <c r="H250">
-        <v>22.82290129773054</v>
+        <v>22.82290129773055</v>
       </c>
       <c r="I250">
         <v>2468007118.23</v>
       </c>
       <c r="J250">
-        <v>28.62557889641439</v>
+        <v>28.6255788964144</v>
       </c>
       <c r="K250">
         <v>1074237714.39</v>
       </c>
       <c r="L250">
-        <v>12.45971951200388</v>
+        <v>12.45971951200389</v>
       </c>
       <c r="M250" s="2">
         <v>43675</v>
@@ -20356,13 +20458,13 @@
         <v>264</v>
       </c>
       <c r="B251">
-        <v>8093877330.2</v>
+        <v>8093877330.200001</v>
       </c>
       <c r="C251">
         <v>335844273.33</v>
       </c>
       <c r="D251">
-        <v>4.1493620378566</v>
+        <v>4.149362037856599</v>
       </c>
       <c r="E251">
         <v>2481415969.47</v>
@@ -20380,7 +20482,7 @@
         <v>2585119244.72</v>
       </c>
       <c r="J251">
-        <v>31.93919476731336</v>
+        <v>31.93919476731335</v>
       </c>
       <c r="K251">
         <v>928763746.4599999</v>
@@ -20444,7 +20546,7 @@
         <v>452007896.59</v>
       </c>
       <c r="D253">
-        <v>5.515366087820104</v>
+        <v>5.515366087820103</v>
       </c>
       <c r="E253">
         <v>2496635436.54</v>
@@ -20520,7 +20622,7 @@
         <v>268</v>
       </c>
       <c r="B255">
-        <v>6406939547.38</v>
+        <v>6406939547.380001</v>
       </c>
       <c r="C255">
         <v>249406029.47</v>
@@ -20532,7 +20634,7 @@
         <v>1936361637.83</v>
       </c>
       <c r="F255">
-        <v>30.22287979323668</v>
+        <v>30.22287979323667</v>
       </c>
       <c r="G255">
         <v>1816284920.45</v>
@@ -20544,7 +20646,7 @@
         <v>1671550632.27</v>
       </c>
       <c r="J255">
-        <v>26.08968946731439</v>
+        <v>26.08968946731438</v>
       </c>
       <c r="K255">
         <v>733336327.36</v>
@@ -20561,13 +20663,13 @@
         <v>269</v>
       </c>
       <c r="B256">
-        <v>8262575591.970001</v>
+        <v>8262575591.969999</v>
       </c>
       <c r="C256">
         <v>265504819.61</v>
       </c>
       <c r="D256">
-        <v>3.213342094782543</v>
+        <v>3.213342094782544</v>
       </c>
       <c r="E256">
         <v>2584213508.6</v>
@@ -20579,7 +20681,7 @@
         <v>2286716477.65</v>
       </c>
       <c r="H256">
-        <v>27.67558919366922</v>
+        <v>27.67558919366923</v>
       </c>
       <c r="I256">
         <v>2021326253.33</v>
@@ -20889,19 +20991,19 @@
         <v>277</v>
       </c>
       <c r="B264">
-        <v>8336799657.45</v>
+        <v>8336799657.450001</v>
       </c>
       <c r="C264">
         <v>392303030.2</v>
       </c>
       <c r="D264">
-        <v>4.705678993370398</v>
+        <v>4.705678993370399</v>
       </c>
       <c r="E264">
         <v>2486846534.95</v>
       </c>
       <c r="F264">
-        <v>29.82975046938646</v>
+        <v>29.82975046938645</v>
       </c>
       <c r="G264">
         <v>2774158101</v>
@@ -20919,7 +21021,7 @@
         <v>903379956.12</v>
       </c>
       <c r="L264">
-        <v>10.83605212118435</v>
+        <v>10.83605212118434</v>
       </c>
       <c r="M264" s="2">
         <v>43773</v>
@@ -20933,10 +21035,10 @@
         <v>8569254332.530001</v>
       </c>
       <c r="C265">
-        <v>526693256.3199999</v>
+        <v>526693256.32</v>
       </c>
       <c r="D265">
-        <v>6.146313738414835</v>
+        <v>6.146313738414836</v>
       </c>
       <c r="E265">
         <v>2356957645.369999</v>
@@ -20974,10 +21076,10 @@
         <v>8842550894.07</v>
       </c>
       <c r="C266">
-        <v>542905402.6999999</v>
+        <v>542905402.7</v>
       </c>
       <c r="D266">
-        <v>6.139692145442823</v>
+        <v>6.139692145442824</v>
       </c>
       <c r="E266">
         <v>2462937389.349999</v>
@@ -21012,10 +21114,10 @@
         <v>280</v>
       </c>
       <c r="B267">
-        <v>7336059148.580001</v>
+        <v>7336059148.58</v>
       </c>
       <c r="C267">
-        <v>487488686.5000001</v>
+        <v>487488686.5</v>
       </c>
       <c r="D267">
         <v>6.645102999126724</v>
@@ -21036,7 +21138,7 @@
         <v>2261245253.9</v>
       </c>
       <c r="J267">
-        <v>30.82370531782989</v>
+        <v>30.8237053178299</v>
       </c>
       <c r="K267">
         <v>689024458.4200001</v>
@@ -21056,10 +21158,10 @@
         <v>9007225995.18</v>
       </c>
       <c r="C268">
-        <v>683932233.1399999</v>
+        <v>683932233.14</v>
       </c>
       <c r="D268">
-        <v>7.593150582720915</v>
+        <v>7.593150582720916</v>
       </c>
       <c r="E268">
         <v>2811862798.610001</v>
@@ -21135,10 +21237,10 @@
         <v>283</v>
       </c>
       <c r="B270">
-        <v>9382716652.200001</v>
+        <v>9382716652.199999</v>
       </c>
       <c r="C270">
-        <v>680605182.39</v>
+        <v>680605182.3899999</v>
       </c>
       <c r="D270">
         <v>7.25381792522122</v>
@@ -21159,13 +21261,13 @@
         <v>2409611437.39</v>
       </c>
       <c r="J270">
-        <v>25.68138340642536</v>
+        <v>25.68138340642537</v>
       </c>
       <c r="K270">
         <v>983941814.21</v>
       </c>
       <c r="L270">
-        <v>10.48674760927893</v>
+        <v>10.48674760927894</v>
       </c>
       <c r="M270" s="2">
         <v>43815</v>
@@ -21179,10 +21281,10 @@
         <v>7690753133.98</v>
       </c>
       <c r="C271">
-        <v>444306569.76</v>
+        <v>444306569.7600001</v>
       </c>
       <c r="D271">
-        <v>5.777152926635019</v>
+        <v>5.77715292663502</v>
       </c>
       <c r="E271">
         <v>2347130086.259999</v>
@@ -21217,7 +21319,7 @@
         <v>285</v>
       </c>
       <c r="B272">
-        <v>7478756584.860001</v>
+        <v>7478756584.86</v>
       </c>
       <c r="C272">
         <v>351149587.9</v>
@@ -21235,7 +21337,7 @@
         <v>2621788500.83</v>
       </c>
       <c r="H272">
-        <v>35.05647591389122</v>
+        <v>35.05647591389123</v>
       </c>
       <c r="I272">
         <v>1733344399.27</v>
@@ -21258,10 +21360,10 @@
         <v>286</v>
       </c>
       <c r="B273">
-        <v>9655819998.829998</v>
+        <v>9655819998.830002</v>
       </c>
       <c r="C273">
-        <v>371653810.47</v>
+        <v>371653810.4700001</v>
       </c>
       <c r="D273">
         <v>3.849013450075017</v>
@@ -21270,19 +21372,19 @@
         <v>2918806335.58</v>
       </c>
       <c r="F273">
-        <v>30.22846672715185</v>
+        <v>30.22846672715184</v>
       </c>
       <c r="G273">
         <v>3027331448.86</v>
       </c>
       <c r="H273">
-        <v>31.35240144520946</v>
+        <v>31.35240144520944</v>
       </c>
       <c r="I273">
         <v>2267717442.22</v>
       </c>
       <c r="J273">
-        <v>23.48549830563102</v>
+        <v>23.485498305631</v>
       </c>
       <c r="K273">
         <v>1070310961.7</v>
@@ -21302,7 +21404,7 @@
         <v>10084810799.07</v>
       </c>
       <c r="C274">
-        <v>276139130.4100001</v>
+        <v>276139130.41</v>
       </c>
       <c r="D274">
         <v>2.738168676753609</v>
@@ -21340,7 +21442,7 @@
         <v>288</v>
       </c>
       <c r="B275">
-        <v>8140209774.799999</v>
+        <v>8140209774.8</v>
       </c>
       <c r="C275">
         <v>232960075.3</v>
@@ -21358,13 +21460,13 @@
         <v>2418818783.28</v>
       </c>
       <c r="H275">
-        <v>29.7144527008142</v>
+        <v>29.71445270081419</v>
       </c>
       <c r="I275">
         <v>2027856695.2</v>
       </c>
       <c r="J275">
-        <v>24.91160241935932</v>
+        <v>24.91160241935931</v>
       </c>
       <c r="K275">
         <v>865590642.7</v>
@@ -21384,10 +21486,10 @@
         <v>10063109183.41</v>
       </c>
       <c r="C276">
-        <v>302963823.5700001</v>
+        <v>302963823.57</v>
       </c>
       <c r="D276">
-        <v>3.010638342963276</v>
+        <v>3.010638342963275</v>
       </c>
       <c r="E276">
         <v>3227542128.18</v>
@@ -21425,7 +21527,7 @@
         <v>10805592431.07</v>
       </c>
       <c r="C277">
-        <v>513006856.1299999</v>
+        <v>513006856.13</v>
       </c>
       <c r="D277">
         <v>4.74760508877717</v>
@@ -21504,25 +21606,25 @@
         <v>292</v>
       </c>
       <c r="B279">
-        <v>9640454536.349998</v>
+        <v>9640454536.35</v>
       </c>
       <c r="C279">
-        <v>753440694.65</v>
+        <v>753440694.6499999</v>
       </c>
       <c r="D279">
-        <v>7.815406335967872</v>
+        <v>7.81540633596787</v>
       </c>
       <c r="E279">
         <v>2730792554.73</v>
       </c>
       <c r="F279">
-        <v>28.32638797717845</v>
+        <v>28.32638797717844</v>
       </c>
       <c r="G279">
         <v>3139331788.82</v>
       </c>
       <c r="H279">
-        <v>32.56414702214438</v>
+        <v>32.56414702214437</v>
       </c>
       <c r="I279">
         <v>1611879230.18</v>
@@ -21551,7 +21653,7 @@
         <v>926730390.3199999</v>
       </c>
       <c r="D280">
-        <v>8.42260106477285</v>
+        <v>8.422601064772852</v>
       </c>
       <c r="E280">
         <v>2760959315.62</v>
@@ -21563,7 +21665,7 @@
         <v>3894240338.2</v>
       </c>
       <c r="H280">
-        <v>35.39285337095613</v>
+        <v>35.39285337095614</v>
       </c>
       <c r="I280">
         <v>2184050092.1</v>
@@ -21589,16 +21691,16 @@
         <v>11089230007.28</v>
       </c>
       <c r="C281">
-        <v>833436809.0900002</v>
+        <v>833436809.09</v>
       </c>
       <c r="D281">
-        <v>7.515732007928909</v>
+        <v>7.515732007928906</v>
       </c>
       <c r="E281">
         <v>2612767084.919999</v>
       </c>
       <c r="F281">
-        <v>23.5613030228856</v>
+        <v>23.56130302288559</v>
       </c>
       <c r="G281">
         <v>4058244060.57</v>
@@ -21630,10 +21732,10 @@
         <v>9682610389.790001</v>
       </c>
       <c r="C282">
-        <v>544497481.03</v>
+        <v>544497481.0299999</v>
       </c>
       <c r="D282">
-        <v>5.62345750898079</v>
+        <v>5.623457508980789</v>
       </c>
       <c r="E282">
         <v>2301719744.16</v>
@@ -21668,13 +21770,13 @@
         <v>296</v>
       </c>
       <c r="B283">
-        <v>7934420289.110001</v>
+        <v>7934420289.11</v>
       </c>
       <c r="C283">
         <v>304974672.6500001</v>
       </c>
       <c r="D283">
-        <v>3.843691933846485</v>
+        <v>3.843691933846486</v>
       </c>
       <c r="E283">
         <v>1949538569.39</v>
@@ -21715,7 +21817,7 @@
         <v>383726758.45</v>
       </c>
       <c r="D284">
-        <v>4.12128127934565</v>
+        <v>4.121281279345649</v>
       </c>
       <c r="E284">
         <v>2147820930.25</v>
@@ -21753,10 +21855,10 @@
         <v>9507262479.91</v>
       </c>
       <c r="C285">
-        <v>382001369.6700001</v>
+        <v>382001369.67</v>
       </c>
       <c r="D285">
-        <v>4.017995405903807</v>
+        <v>4.017995405903806</v>
       </c>
       <c r="E285">
         <v>2291531494.67</v>
@@ -21791,19 +21893,19 @@
         <v>299</v>
       </c>
       <c r="B286">
-        <v>8384202889.749999</v>
+        <v>8384202889.750001</v>
       </c>
       <c r="C286">
         <v>161678287.63</v>
       </c>
       <c r="D286">
-        <v>1.928368024438647</v>
+        <v>1.928368024438646</v>
       </c>
       <c r="E286">
         <v>1873595487.04</v>
       </c>
       <c r="F286">
-        <v>22.34673363320609</v>
+        <v>22.34673363320608</v>
       </c>
       <c r="G286">
         <v>3472017707.66</v>
@@ -21815,7 +21917,7 @@
         <v>1653051346.35</v>
       </c>
       <c r="J286">
-        <v>19.71626126045825</v>
+        <v>19.71626126045824</v>
       </c>
       <c r="K286">
         <v>1223860061.07</v>
@@ -21917,22 +22019,22 @@
         <v>14314502680.3</v>
       </c>
       <c r="C289">
-        <v>580423914.3300002</v>
+        <v>580423914.33</v>
       </c>
       <c r="D289">
-        <v>4.054796225151399</v>
+        <v>4.054796225151397</v>
       </c>
       <c r="E289">
         <v>2599864747.92</v>
       </c>
       <c r="F289">
-        <v>18.16245248602317</v>
+        <v>18.16245248602316</v>
       </c>
       <c r="G289">
         <v>6616430623.89</v>
       </c>
       <c r="H289">
-        <v>46.22186862974785</v>
+        <v>46.22186862974784</v>
       </c>
       <c r="I289">
         <v>2855961929.56</v>
@@ -21958,10 +22060,10 @@
         <v>14999693120.48</v>
       </c>
       <c r="C290">
-        <v>625853596.5500001</v>
+        <v>625853596.55</v>
       </c>
       <c r="D290">
-        <v>4.172442672813645</v>
+        <v>4.172442672813643</v>
       </c>
       <c r="E290">
         <v>2587181184.180001</v>
@@ -21999,10 +22101,10 @@
         <v>15789857137.27</v>
       </c>
       <c r="C291">
-        <v>640461948.65</v>
+        <v>640461948.6500001</v>
       </c>
       <c r="D291">
-        <v>4.056160502796881</v>
+        <v>4.056160502796882</v>
       </c>
       <c r="E291">
         <v>3023411048.36</v>
@@ -22084,19 +22186,19 @@
         <v>427925274.4</v>
       </c>
       <c r="D293">
-        <v>2.964801799260757</v>
+        <v>2.964801799260758</v>
       </c>
       <c r="E293">
         <v>3054147266.76</v>
       </c>
       <c r="F293">
-        <v>21.16009932900886</v>
+        <v>21.16009932900887</v>
       </c>
       <c r="G293">
         <v>5078715611.44</v>
       </c>
       <c r="H293">
-        <v>35.18694988007702</v>
+        <v>35.18694988007703</v>
       </c>
       <c r="I293">
         <v>3321687353.46</v>
@@ -22122,10 +22224,10 @@
         <v>19266050631.53</v>
       </c>
       <c r="C294">
-        <v>739915045.16</v>
+        <v>739915045.1600001</v>
       </c>
       <c r="D294">
-        <v>3.840512304836812</v>
+        <v>3.840512304836813</v>
       </c>
       <c r="E294">
         <v>3983945643.23</v>
@@ -22163,10 +22265,10 @@
         <v>19730610646.15</v>
       </c>
       <c r="C295">
-        <v>745488169.73</v>
+        <v>745488169.7299999</v>
       </c>
       <c r="D295">
-        <v>3.778332982691876</v>
+        <v>3.778332982691875</v>
       </c>
       <c r="E295">
         <v>5294687713.8</v>
@@ -22204,7 +22306,7 @@
         <v>21040357731.21</v>
       </c>
       <c r="C296">
-        <v>598870923.26</v>
+        <v>598870923.2599999</v>
       </c>
       <c r="D296">
         <v>2.846296298335607</v>
@@ -22245,7 +22347,7 @@
         <v>23067882477.79</v>
       </c>
       <c r="C297">
-        <v>503435498.22</v>
+        <v>503435498.2200001</v>
       </c>
       <c r="D297">
         <v>2.182408804556348</v>
@@ -22286,7 +22388,7 @@
         <v>19428159940.33</v>
       </c>
       <c r="C298">
-        <v>438196745.8299999</v>
+        <v>438196745.83</v>
       </c>
       <c r="D298">
         <v>2.255472196933936</v>
@@ -22295,13 +22397,13 @@
         <v>5681957437.429999</v>
       </c>
       <c r="F298">
-        <v>29.24598857988138</v>
+        <v>29.24598857988137</v>
       </c>
       <c r="G298">
         <v>5667468987.280001</v>
       </c>
       <c r="H298">
-        <v>29.17141409524414</v>
+        <v>29.17141409524413</v>
       </c>
       <c r="I298">
         <v>2151018427.92</v>
@@ -22313,7 +22415,7 @@
         <v>5489518341.870001</v>
       </c>
       <c r="L298">
-        <v>28.25547225640535</v>
+        <v>28.25547225640534</v>
       </c>
       <c r="M298" s="2">
         <v>44011</v>
@@ -22327,7 +22429,7 @@
         <v>27953689541.52</v>
       </c>
       <c r="C299">
-        <v>942514883.1700001</v>
+        <v>942514883.1699998</v>
       </c>
       <c r="D299">
         <v>3.371701190893137</v>
@@ -22412,19 +22514,19 @@
         <v>1732036432.49</v>
       </c>
       <c r="D301">
-        <v>5.684278700162047</v>
+        <v>5.684278700162048</v>
       </c>
       <c r="E301">
         <v>9001991837</v>
       </c>
       <c r="F301">
-        <v>29.54316058151804</v>
+        <v>29.54316058151805</v>
       </c>
       <c r="G301">
         <v>8110879029.39</v>
       </c>
       <c r="H301">
-        <v>26.61866462016166</v>
+        <v>26.61866462016167</v>
       </c>
       <c r="I301">
         <v>3749878143.26</v>
@@ -22488,19 +22590,19 @@
         <v>316</v>
       </c>
       <c r="B303">
-        <v>32798677193.03</v>
+        <v>32798677193.03001</v>
       </c>
       <c r="C303">
         <v>1478796141.21</v>
       </c>
       <c r="D303">
-        <v>4.508706654560621</v>
+        <v>4.50870665456062</v>
       </c>
       <c r="E303">
         <v>11133160713.53</v>
       </c>
       <c r="F303">
-        <v>33.94393209216344</v>
+        <v>33.94393209216343</v>
       </c>
       <c r="G303">
         <v>8299058034.519999</v>
@@ -22512,7 +22614,7 @@
         <v>5237119990.700001</v>
       </c>
       <c r="J303">
-        <v>15.96747319984275</v>
+        <v>15.96747319984274</v>
       </c>
       <c r="K303">
         <v>6650542313.070001</v>
@@ -22617,7 +22719,7 @@
         <v>1380223101.69</v>
       </c>
       <c r="D306">
-        <v>3.557666937108945</v>
+        <v>3.557666937108944</v>
       </c>
       <c r="E306">
         <v>14633125653.36</v>
@@ -22699,7 +22801,7 @@
         <v>2732524682.81</v>
       </c>
       <c r="D308">
-        <v>8.803235771584999</v>
+        <v>8.803235771585001</v>
       </c>
       <c r="E308">
         <v>10126056794.84</v>
@@ -22822,7 +22924,7 @@
         <v>3907236257.67</v>
       </c>
       <c r="D311">
-        <v>8.76619010760691</v>
+        <v>8.766190107606908</v>
       </c>
       <c r="E311">
         <v>14743454866.51</v>
@@ -22898,25 +23000,25 @@
         <v>326</v>
       </c>
       <c r="B313">
-        <v>52195439914.55999</v>
+        <v>52195439914.56</v>
       </c>
       <c r="C313">
         <v>4615977774.96</v>
       </c>
       <c r="D313">
-        <v>8.843641863189598</v>
+        <v>8.843641863189596</v>
       </c>
       <c r="E313">
         <v>16459174894.68</v>
       </c>
       <c r="F313">
-        <v>31.53374111152705</v>
+        <v>31.53374111152704</v>
       </c>
       <c r="G313">
         <v>12168407452.84</v>
       </c>
       <c r="H313">
-        <v>23.31316197882185</v>
+        <v>23.31316197882184</v>
       </c>
       <c r="I313">
         <v>9200897337.26</v>
@@ -22939,25 +23041,25 @@
         <v>327</v>
       </c>
       <c r="B314">
-        <v>52120664010.1</v>
+        <v>52120664010.10001</v>
       </c>
       <c r="C314">
         <v>4684902654.179999</v>
       </c>
       <c r="D314">
-        <v>8.988570547129166</v>
+        <v>8.988570547129164</v>
       </c>
       <c r="E314">
         <v>17314880509.15</v>
       </c>
       <c r="F314">
-        <v>33.22075963152485</v>
+        <v>33.22075963152484</v>
       </c>
       <c r="G314">
         <v>12125234634.94</v>
       </c>
       <c r="H314">
-        <v>23.26377621089087</v>
+        <v>23.26377621089086</v>
       </c>
       <c r="I314">
         <v>8653031672.34</v>
@@ -22980,7 +23082,7 @@
         <v>328</v>
       </c>
       <c r="B315">
-        <v>50446451035.85001</v>
+        <v>50446451035.85</v>
       </c>
       <c r="C315">
         <v>5101930203.72</v>
@@ -22992,7 +23094,7 @@
         <v>16778424053.81</v>
       </c>
       <c r="F315">
-        <v>33.25987003899706</v>
+        <v>33.25987003899707</v>
       </c>
       <c r="G315">
         <v>10713398244.63</v>
@@ -23027,7 +23129,7 @@
         <v>5570059652.53</v>
       </c>
       <c r="D316">
-        <v>10.75655528706878</v>
+        <v>10.75655528706877</v>
       </c>
       <c r="E316">
         <v>15206100995.8</v>
@@ -23039,7 +23141,7 @@
         <v>13931602540.47</v>
       </c>
       <c r="H316">
-        <v>26.90385064295795</v>
+        <v>26.90385064295794</v>
       </c>
       <c r="I316">
         <v>11913158868.79</v>
@@ -23051,7 +23153,7 @@
         <v>5162009409.57</v>
       </c>
       <c r="L316">
-        <v>9.968553852235409</v>
+        <v>9.968553852235408</v>
       </c>
       <c r="M316" s="2">
         <v>44137</v>
@@ -23065,10 +23167,10 @@
         <v>53929857105.50999</v>
       </c>
       <c r="C317">
-        <v>4874422197.780001</v>
+        <v>4874422197.78</v>
       </c>
       <c r="D317">
-        <v>9.038448198079841</v>
+        <v>9.038448198079839</v>
       </c>
       <c r="E317">
         <v>17513861700.3</v>
@@ -23106,10 +23208,10 @@
         <v>57220525775.25</v>
       </c>
       <c r="C318">
-        <v>4920840458.129999</v>
+        <v>4920840458.13</v>
       </c>
       <c r="D318">
-        <v>8.599781968900476</v>
+        <v>8.599781968900478</v>
       </c>
       <c r="E318">
         <v>19634646903.2</v>
@@ -23185,10 +23287,10 @@
         <v>333</v>
       </c>
       <c r="B320">
-        <v>67326378311.33</v>
+        <v>67326378311.32999</v>
       </c>
       <c r="C320">
-        <v>7430149687.61</v>
+        <v>7430149687.610001</v>
       </c>
       <c r="D320">
         <v>11.03601571029348</v>
@@ -23197,25 +23299,25 @@
         <v>23696482103.32</v>
       </c>
       <c r="F320">
-        <v>35.19643072696255</v>
+        <v>35.19643072696256</v>
       </c>
       <c r="G320">
         <v>12459118467.17</v>
       </c>
       <c r="H320">
-        <v>18.50555277094612</v>
+        <v>18.50555277094613</v>
       </c>
       <c r="I320">
         <v>16809677143.71</v>
       </c>
       <c r="J320">
-        <v>24.96744599268187</v>
+        <v>24.96744599268188</v>
       </c>
       <c r="K320">
         <v>6930950909.52</v>
       </c>
       <c r="L320">
-        <v>10.29455479911597</v>
+        <v>10.29455479911598</v>
       </c>
       <c r="M320" s="2">
         <v>44165</v>
@@ -23226,25 +23328,25 @@
         <v>334</v>
       </c>
       <c r="B321">
-        <v>75937678864.02</v>
+        <v>75937678864.01999</v>
       </c>
       <c r="C321">
-        <v>9030927095.609999</v>
+        <v>9030927095.610001</v>
       </c>
       <c r="D321">
-        <v>11.89255087949355</v>
+        <v>11.89255087949356</v>
       </c>
       <c r="E321">
         <v>27705215278.04</v>
       </c>
       <c r="F321">
-        <v>36.48414817583658</v>
+        <v>36.48414817583659</v>
       </c>
       <c r="G321">
         <v>12632547383.25</v>
       </c>
       <c r="H321">
-        <v>16.63541416096064</v>
+        <v>16.63541416096065</v>
       </c>
       <c r="I321">
         <v>18808173774.62</v>
@@ -23256,7 +23358,7 @@
         <v>7760815332.499999</v>
       </c>
       <c r="L321">
-        <v>10.21997965778902</v>
+        <v>10.21997965778903</v>
       </c>
       <c r="M321" s="2">
         <v>44172</v>
@@ -23267,7 +23369,7 @@
         <v>335</v>
       </c>
       <c r="B322">
-        <v>82520556192.92</v>
+        <v>82520556192.92001</v>
       </c>
       <c r="C322">
         <v>9669347400.66</v>
@@ -23291,13 +23393,13 @@
         <v>17721171836.12</v>
       </c>
       <c r="J322">
-        <v>21.47485748240803</v>
+        <v>21.47485748240802</v>
       </c>
       <c r="K322">
         <v>8509361252.61</v>
       </c>
       <c r="L322">
-        <v>10.31180792421765</v>
+        <v>10.31180792421764</v>
       </c>
       <c r="M322" s="2">
         <v>44179</v>
@@ -23352,10 +23454,10 @@
         <v>72564921470.41</v>
       </c>
       <c r="C324">
-        <v>5763147990.260001</v>
+        <v>5763147990.26</v>
       </c>
       <c r="D324">
-        <v>7.942057778716202</v>
+        <v>7.942057778716201</v>
       </c>
       <c r="E324">
         <v>29813678491.37</v>
@@ -23437,19 +23539,19 @@
         <v>9124267990.009998</v>
       </c>
       <c r="D326">
-        <v>8.403945149212682</v>
+        <v>8.403945149212683</v>
       </c>
       <c r="E326">
         <v>50718921501.00999</v>
       </c>
       <c r="F326">
-        <v>46.71487452893683</v>
+        <v>46.71487452893684</v>
       </c>
       <c r="G326">
         <v>23462694377.38</v>
       </c>
       <c r="H326">
-        <v>21.61041267268019</v>
+        <v>21.6104126726802</v>
       </c>
       <c r="I326">
         <v>11184957518.68</v>
@@ -23461,7 +23563,7 @@
         <v>14080404950.3</v>
       </c>
       <c r="L326">
-        <v>12.96881580095876</v>
+        <v>12.96881580095877</v>
       </c>
       <c r="M326" s="2">
         <v>44207</v>
@@ -23516,10 +23618,10 @@
         <v>116294279243.43</v>
       </c>
       <c r="C328">
-        <v>9193608290.570002</v>
+        <v>9193608290.57</v>
       </c>
       <c r="D328">
-        <v>7.905469082727379</v>
+        <v>7.905469082727377</v>
       </c>
       <c r="E328">
         <v>53376771531.19</v>
@@ -23584,7 +23686,7 @@
         <v>11909302937.53</v>
       </c>
       <c r="L329">
-        <v>9.657076061297733</v>
+        <v>9.657076061297731</v>
       </c>
       <c r="M329" s="2">
         <v>44228</v>
@@ -23601,7 +23703,7 @@
         <v>13138419391.12</v>
       </c>
       <c r="D330">
-        <v>9.666418452804132</v>
+        <v>9.666418452804134</v>
       </c>
       <c r="E330">
         <v>61902442704.89</v>
@@ -23642,7 +23744,7 @@
         <v>10144387000.33</v>
       </c>
       <c r="D331">
-        <v>9.190825775656872</v>
+        <v>9.190825775656874</v>
       </c>
       <c r="E331">
         <v>50254055759.38</v>
@@ -23841,7 +23943,7 @@
         <v>349</v>
       </c>
       <c r="B336">
-        <v>90951361545.08</v>
+        <v>90951361545.08002</v>
       </c>
       <c r="C336">
         <v>10806653940.72</v>
@@ -23853,7 +23955,7 @@
         <v>31618494728.99</v>
       </c>
       <c r="F336">
-        <v>34.76417965806736</v>
+        <v>34.76417965806735</v>
       </c>
       <c r="G336">
         <v>22552821308.16</v>
@@ -23865,7 +23967,7 @@
         <v>16328314028</v>
       </c>
       <c r="J336">
-        <v>17.95279779281466</v>
+        <v>17.95279779281465</v>
       </c>
       <c r="K336">
         <v>9645077539.209999</v>
@@ -23885,7 +23987,7 @@
         <v>87130682351.96001</v>
       </c>
       <c r="C337">
-        <v>9325669156.380001</v>
+        <v>9325669156.379999</v>
       </c>
       <c r="D337">
         <v>10.70308289186745</v>
@@ -24058,7 +24160,7 @@
         <v>37120059764.9</v>
       </c>
       <c r="F341">
-        <v>30.74009221329198</v>
+        <v>30.74009221329197</v>
       </c>
       <c r="G341">
         <v>36074033477.39999</v>
@@ -24070,7 +24172,7 @@
         <v>17666295382.43</v>
       </c>
       <c r="J341">
-        <v>14.62992119524179</v>
+        <v>14.62992119524178</v>
       </c>
       <c r="K341">
         <v>11962164904.86</v>
@@ -24128,7 +24230,7 @@
         <v>356</v>
       </c>
       <c r="B343">
-        <v>98084680712.23</v>
+        <v>98084680712.22998</v>
       </c>
       <c r="C343">
         <v>12408828443.75</v>
@@ -24216,7 +24318,7 @@
         <v>11850964478.06</v>
       </c>
       <c r="D345">
-        <v>11.28681325238008</v>
+        <v>11.28681325238007</v>
       </c>
       <c r="E345">
         <v>31925499337.06</v>
@@ -24251,7 +24353,7 @@
         <v>359</v>
       </c>
       <c r="B346">
-        <v>83080701664.79001</v>
+        <v>83080701664.78999</v>
       </c>
       <c r="C346">
         <v>9771323167.879999</v>
@@ -24304,13 +24406,13 @@
         <v>30911693567.91</v>
       </c>
       <c r="F347">
-        <v>28.91914120279797</v>
+        <v>28.91914120279796</v>
       </c>
       <c r="G347">
         <v>41921897837.02</v>
       </c>
       <c r="H347">
-        <v>39.21963319074209</v>
+        <v>39.21963319074208</v>
       </c>
       <c r="I347">
         <v>12445314612.13</v>
@@ -24322,7 +24424,7 @@
         <v>10457550300.69</v>
       </c>
       <c r="L347">
-        <v>9.783461818959273</v>
+        <v>9.783461818959271</v>
       </c>
       <c r="M347" s="2">
         <v>44354</v>
@@ -24345,7 +24447,7 @@
         <v>31567800520.58</v>
       </c>
       <c r="F348">
-        <v>28.6297412458943</v>
+        <v>28.62974124589431</v>
       </c>
       <c r="G348">
         <v>44537352469.04</v>
@@ -24456,25 +24558,25 @@
         <v>364</v>
       </c>
       <c r="B351">
-        <v>95227793500.28</v>
+        <v>95227793500.27998</v>
       </c>
       <c r="C351">
-        <v>9284060248.389997</v>
+        <v>9284060248.389999</v>
       </c>
       <c r="D351">
-        <v>9.749317827428921</v>
+        <v>9.749317827428925</v>
       </c>
       <c r="E351">
         <v>24552087271.94001</v>
       </c>
       <c r="F351">
-        <v>25.78248048125552</v>
+        <v>25.78248048125553</v>
       </c>
       <c r="G351">
         <v>40749909035.78999</v>
       </c>
       <c r="H351">
-        <v>42.79203322680177</v>
+        <v>42.79203322680178</v>
       </c>
       <c r="I351">
         <v>11338329669.64</v>
@@ -24486,7 +24588,7 @@
         <v>9303407274.52</v>
       </c>
       <c r="L351">
-        <v>9.769634402473732</v>
+        <v>9.769634402473734</v>
       </c>
       <c r="M351" s="2">
         <v>44382</v>
@@ -24544,7 +24646,7 @@
         <v>11189443850.44</v>
       </c>
       <c r="D353">
-        <v>9.806532170869616</v>
+        <v>9.806532170869611</v>
       </c>
       <c r="E353">
         <v>27516708919.65</v>
@@ -24585,7 +24687,7 @@
         <v>11305928009.79</v>
       </c>
       <c r="D354">
-        <v>9.982689599722097</v>
+        <v>9.982689599722091</v>
       </c>
       <c r="E354">
         <v>28085773821.85</v>
@@ -24626,7 +24728,7 @@
         <v>11661761263.12</v>
       </c>
       <c r="D355">
-        <v>10.15642416826548</v>
+        <v>10.15642416826547</v>
       </c>
       <c r="E355">
         <v>30059529898.2</v>
@@ -24755,13 +24857,13 @@
         <v>25587001530.85</v>
       </c>
       <c r="F358">
-        <v>23.18928659367718</v>
+        <v>23.18928659367717</v>
       </c>
       <c r="G358">
         <v>49942972144.81998</v>
       </c>
       <c r="H358">
-        <v>45.26290011003854</v>
+        <v>45.26290011003853</v>
       </c>
       <c r="I358">
         <v>12021698511.9</v>
@@ -24872,7 +24974,7 @@
         <v>11201854089.52</v>
       </c>
       <c r="D361">
-        <v>10.50950162560951</v>
+        <v>10.5095016256095</v>
       </c>
       <c r="E361">
         <v>21412268815.66</v>
@@ -24884,7 +24986,7 @@
         <v>49455147628.86</v>
       </c>
       <c r="H361">
-        <v>46.39847566721283</v>
+        <v>46.39847566721284</v>
       </c>
       <c r="I361">
         <v>13291097815.97</v>
@@ -24951,10 +25053,10 @@
         <v>99340481235.62</v>
       </c>
       <c r="C363">
-        <v>9412458324.219999</v>
+        <v>9412458324.220001</v>
       </c>
       <c r="D363">
-        <v>9.474947380106936</v>
+        <v>9.474947380106938</v>
       </c>
       <c r="E363">
         <v>18248359329.42</v>
@@ -24989,13 +25091,13 @@
         <v>377</v>
       </c>
       <c r="B364">
-        <v>98478030797.93999</v>
+        <v>98478030797.94</v>
       </c>
       <c r="C364">
         <v>9082644027.779999</v>
       </c>
       <c r="D364">
-        <v>9.223015482931443</v>
+        <v>9.223015482931441</v>
       </c>
       <c r="E364">
         <v>17613145290.28</v>
@@ -25007,7 +25109,7 @@
         <v>41174775063.9</v>
       </c>
       <c r="H364">
-        <v>41.81112754821791</v>
+        <v>41.8111275482179</v>
       </c>
       <c r="I364">
         <v>20766209035.98</v>
@@ -25019,7 +25121,7 @@
         <v>9841257380</v>
       </c>
       <c r="L364">
-        <v>9.993353136998211</v>
+        <v>9.993353136998209</v>
       </c>
       <c r="M364" s="2">
         <v>44473</v>
@@ -25033,7 +25135,7 @@
         <v>100724038815.74</v>
       </c>
       <c r="C365">
-        <v>8415292509.219999</v>
+        <v>8415292509.22</v>
       </c>
       <c r="D365">
         <v>8.354800510546005</v>
@@ -25077,7 +25179,7 @@
         <v>8561471198.73</v>
       </c>
       <c r="D366">
-        <v>8.094225000683737</v>
+        <v>8.094225000683736</v>
       </c>
       <c r="E366">
         <v>20498565663.61</v>
@@ -25115,7 +25217,7 @@
         <v>107023893989.29</v>
       </c>
       <c r="C367">
-        <v>8671043117.990002</v>
+        <v>8671043117.99</v>
       </c>
       <c r="D367">
         <v>8.101969377845402</v>
@@ -25124,19 +25226,19 @@
         <v>21758588614.65</v>
       </c>
       <c r="F367">
-        <v>20.33058955678383</v>
+        <v>20.33058955678384</v>
       </c>
       <c r="G367">
         <v>40565004437.48</v>
       </c>
       <c r="H367">
-        <v>37.90275510022031</v>
+        <v>37.90275510022032</v>
       </c>
       <c r="I367">
         <v>24538730600.44</v>
       </c>
       <c r="J367">
-        <v>22.92827301060043</v>
+        <v>22.92827301060044</v>
       </c>
       <c r="K367">
         <v>11490527218.73</v>
@@ -25156,10 +25258,10 @@
         <v>109115958205.44</v>
       </c>
       <c r="C368">
-        <v>8966234390.18</v>
+        <v>8966234390.180002</v>
       </c>
       <c r="D368">
-        <v>8.217161392010748</v>
+        <v>8.21716139201075</v>
       </c>
       <c r="E368">
         <v>21601273369.23</v>
@@ -25197,10 +25299,10 @@
         <v>103954877182.61</v>
       </c>
       <c r="C369">
-        <v>9125025225.809999</v>
+        <v>9125025225.809998</v>
       </c>
       <c r="D369">
-        <v>8.777871200579391</v>
+        <v>8.777871200579389</v>
       </c>
       <c r="E369">
         <v>18754832369.26</v>
@@ -25238,7 +25340,7 @@
         <v>101487749083.05</v>
       </c>
       <c r="C370">
-        <v>8500713226.200001</v>
+        <v>8500713226.200002</v>
       </c>
       <c r="D370">
         <v>8.376097906402133</v>
@@ -25253,13 +25355,13 @@
         <v>37358274793.04</v>
       </c>
       <c r="H370">
-        <v>36.81062505629993</v>
+        <v>36.81062505629992</v>
       </c>
       <c r="I370">
         <v>23342468322.28</v>
       </c>
       <c r="J370">
-        <v>23.00028184010493</v>
+        <v>23.00028184010492</v>
       </c>
       <c r="K370">
         <v>10480609222.82</v>
@@ -25276,25 +25378,25 @@
         <v>384</v>
       </c>
       <c r="B371">
-        <v>75260428317.67</v>
+        <v>75260428317.66998</v>
       </c>
       <c r="C371">
         <v>6111807503.29</v>
       </c>
       <c r="D371">
-        <v>8.120877916735216</v>
+        <v>8.120877916735218</v>
       </c>
       <c r="E371">
         <v>14437992643.11</v>
       </c>
       <c r="F371">
-        <v>19.18404261821106</v>
+        <v>19.18404261821107</v>
       </c>
       <c r="G371">
         <v>29215291499.29</v>
       </c>
       <c r="H371">
-        <v>38.81892802413229</v>
+        <v>38.8189280241323</v>
       </c>
       <c r="I371">
         <v>17417660687.75</v>
@@ -25306,7 +25408,7 @@
         <v>8077675984.23</v>
       </c>
       <c r="L371">
-        <v>10.73296573616959</v>
+        <v>10.7329657361696</v>
       </c>
       <c r="M371" s="2">
         <v>44522</v>
@@ -25317,25 +25419,25 @@
         <v>385</v>
       </c>
       <c r="B372">
-        <v>89712419242.14</v>
+        <v>89712419242.13998</v>
       </c>
       <c r="C372">
         <v>7722190074.860001</v>
       </c>
       <c r="D372">
-        <v>8.607715787952699</v>
+        <v>8.607715787952701</v>
       </c>
       <c r="E372">
         <v>16565981564.32</v>
       </c>
       <c r="F372">
-        <v>18.46565024582301</v>
+        <v>18.46565024582302</v>
       </c>
       <c r="G372">
         <v>33194471375.84</v>
       </c>
       <c r="H372">
-        <v>37.00097673906868</v>
+        <v>37.00097673906869</v>
       </c>
       <c r="I372">
         <v>23144349514.9</v>
@@ -25347,7 +25449,7 @@
         <v>9085426712.219999</v>
       </c>
       <c r="L372">
-        <v>10.12727868557173</v>
+        <v>10.12727868557174</v>
       </c>
       <c r="M372" s="2">
         <v>44529</v>
@@ -25358,13 +25460,13 @@
         <v>386</v>
       </c>
       <c r="B373">
-        <v>84174501467.29001</v>
+        <v>84174501467.28999</v>
       </c>
       <c r="C373">
         <v>6736010953.509999</v>
       </c>
       <c r="D373">
-        <v>8.002436410184853</v>
+        <v>8.002436410184854</v>
       </c>
       <c r="E373">
         <v>15906602753.38</v>
@@ -25388,7 +25490,7 @@
         <v>7295611794.5</v>
       </c>
       <c r="L373">
-        <v>8.667246811476579</v>
+        <v>8.667246811476581</v>
       </c>
       <c r="M373" s="2">
         <v>44536</v>
@@ -25525,10 +25627,10 @@
         <v>76992953469.31</v>
       </c>
       <c r="C377">
-        <v>5552397832.369999</v>
+        <v>5552397832.37</v>
       </c>
       <c r="D377">
-        <v>7.211566230646326</v>
+        <v>7.211566230646328</v>
       </c>
       <c r="E377">
         <v>16022770240.61</v>
@@ -25563,13 +25665,13 @@
         <v>391</v>
       </c>
       <c r="B378">
-        <v>71326641227.52</v>
+        <v>71326641227.51999</v>
       </c>
       <c r="C378">
-        <v>4443911638.679999</v>
+        <v>4443911638.68</v>
       </c>
       <c r="D378">
-        <v>6.230367170248026</v>
+        <v>6.230367170248028</v>
       </c>
       <c r="E378">
         <v>13499977222.77</v>
@@ -25587,13 +25689,13 @@
         <v>16786230278.17</v>
       </c>
       <c r="J378">
-        <v>23.53430638157311</v>
+        <v>23.53430638157312</v>
       </c>
       <c r="K378">
         <v>6091876040.299999</v>
       </c>
       <c r="L378">
-        <v>8.54081439341569</v>
+        <v>8.540814393415694</v>
       </c>
       <c r="M378" s="2">
         <v>44571</v>
@@ -25607,10 +25709,10 @@
         <v>51467819236.2</v>
       </c>
       <c r="C379">
-        <v>3666417490.06</v>
+        <v>3666417490.059999</v>
       </c>
       <c r="D379">
-        <v>7.12370864837657</v>
+        <v>7.123708648376572</v>
       </c>
       <c r="E379">
         <v>9751552953.779999</v>
@@ -25634,7 +25736,7 @@
         <v>4270573240.08</v>
       </c>
       <c r="L379">
-        <v>8.297560113206201</v>
+        <v>8.297560113206202</v>
       </c>
       <c r="M379" s="2">
         <v>44578</v>
@@ -25648,7 +25750,7 @@
         <v>59816312065.59</v>
       </c>
       <c r="C380">
-        <v>3612107607.76</v>
+        <v>3612107607.760001</v>
       </c>
       <c r="D380">
         <v>6.038666515914989</v>
@@ -25686,25 +25788,25 @@
         <v>394</v>
       </c>
       <c r="B381">
-        <v>61705239328.69</v>
+        <v>61705239328.68999</v>
       </c>
       <c r="C381">
         <v>3634639188.96</v>
       </c>
       <c r="D381">
-        <v>5.890325081795876</v>
+        <v>5.890325081795877</v>
       </c>
       <c r="E381">
         <v>12386816442.24</v>
       </c>
       <c r="F381">
-        <v>20.07417291789146</v>
+        <v>20.07417291789147</v>
       </c>
       <c r="G381">
         <v>24969840137.41</v>
       </c>
       <c r="H381">
-        <v>40.46632086523682</v>
+        <v>40.46632086523683</v>
       </c>
       <c r="I381">
         <v>15652912253.85</v>
@@ -25716,7 +25818,7 @@
         <v>5061031306.23</v>
       </c>
       <c r="L381">
-        <v>8.20194745420404</v>
+        <v>8.201947454204044</v>
       </c>
       <c r="M381" s="2">
         <v>44592</v>
@@ -25730,10 +25832,10 @@
         <v>61793579403.97</v>
       </c>
       <c r="C382">
-        <v>4394912838.89</v>
+        <v>4394912838.889998</v>
       </c>
       <c r="D382">
-        <v>7.112248361854312</v>
+        <v>7.112248361854309</v>
       </c>
       <c r="E382">
         <v>10136125380.62</v>
@@ -25856,7 +25958,7 @@
         <v>2470386747.67</v>
       </c>
       <c r="D385">
-        <v>4.100597374473346</v>
+        <v>4.100597374473345</v>
       </c>
       <c r="E385">
         <v>10525979668.45</v>
@@ -25897,7 +25999,7 @@
         <v>2309118672.59</v>
       </c>
       <c r="D386">
-        <v>4.250781133734064</v>
+        <v>4.250781133734063</v>
       </c>
       <c r="E386">
         <v>10794893786.53</v>
@@ -25935,10 +26037,10 @@
         <v>53716555714.54</v>
       </c>
       <c r="C387">
-        <v>2667013293.88</v>
+        <v>2667013293.880001</v>
       </c>
       <c r="D387">
-        <v>4.964974500697729</v>
+        <v>4.96497450069773</v>
       </c>
       <c r="E387">
         <v>10305590321.39</v>
@@ -25973,7 +26075,7 @@
         <v>401</v>
       </c>
       <c r="B388">
-        <v>61872898698.49</v>
+        <v>61872898698.49001</v>
       </c>
       <c r="C388">
         <v>3090151990</v>
@@ -25991,13 +26093,13 @@
         <v>21555689620.11</v>
       </c>
       <c r="H388">
-        <v>34.83866130977967</v>
+        <v>34.83866130977966</v>
       </c>
       <c r="I388">
         <v>19039355968.17</v>
       </c>
       <c r="J388">
-        <v>30.77172133303438</v>
+        <v>30.77172133303437</v>
       </c>
       <c r="K388">
         <v>6400346250.96</v>
@@ -26017,7 +26119,7 @@
         <v>61663648838.34</v>
       </c>
       <c r="C389">
-        <v>2988332641.389999</v>
+        <v>2988332641.39</v>
       </c>
       <c r="D389">
         <v>4.84618198515034</v>
@@ -26055,13 +26157,13 @@
         <v>403</v>
       </c>
       <c r="B390">
-        <v>59631856165.79</v>
+        <v>59631856165.79001</v>
       </c>
       <c r="C390">
-        <v>2972879131.66</v>
+        <v>2972879131.659999</v>
       </c>
       <c r="D390">
-        <v>4.985387547546274</v>
+        <v>4.985387547546273</v>
       </c>
       <c r="E390">
         <v>11824855476.33</v>
@@ -26073,7 +26175,7 @@
         <v>17238314398.59</v>
       </c>
       <c r="H390">
-        <v>28.90789505304615</v>
+        <v>28.90789505304614</v>
       </c>
       <c r="I390">
         <v>21700084462.11</v>
@@ -26085,7 +26187,7 @@
         <v>5895722697.1</v>
       </c>
       <c r="L390">
-        <v>9.886867651257681</v>
+        <v>9.886867651257679</v>
       </c>
       <c r="M390" s="2">
         <v>44655</v>
@@ -26096,13 +26198,13 @@
         <v>404</v>
       </c>
       <c r="B391">
-        <v>43380805312.32999</v>
+        <v>43380805312.33</v>
       </c>
       <c r="C391">
         <v>2306117552.87</v>
       </c>
       <c r="D391">
-        <v>5.315986036373878</v>
+        <v>5.315986036373877</v>
       </c>
       <c r="E391">
         <v>8413856244.790001</v>
@@ -26120,7 +26222,7 @@
         <v>15847985563.25</v>
       </c>
       <c r="J391">
-        <v>36.53225303022573</v>
+        <v>36.53225303022572</v>
       </c>
       <c r="K391">
         <v>4334386588.36</v>
@@ -26143,13 +26245,13 @@
         <v>2604635055.98</v>
       </c>
       <c r="D392">
-        <v>4.988267784370804</v>
+        <v>4.988267784370805</v>
       </c>
       <c r="E392">
         <v>10245749596.22</v>
       </c>
       <c r="F392">
-        <v>19.62215110336242</v>
+        <v>19.62215110336243</v>
       </c>
       <c r="G392">
         <v>14627172976.04</v>
@@ -26161,7 +26263,7 @@
         <v>19424467971.73</v>
       </c>
       <c r="J392">
-        <v>37.20077697236801</v>
+        <v>37.20077697236802</v>
       </c>
       <c r="K392">
         <v>5313195566.4</v>
@@ -26181,7 +26283,7 @@
         <v>47368832764.3</v>
       </c>
       <c r="C393">
-        <v>2249550232.81</v>
+        <v>2249550232.809999</v>
       </c>
       <c r="D393">
         <v>4.749009214568183</v>
@@ -26266,19 +26368,19 @@
         <v>2361513367.6</v>
       </c>
       <c r="D395">
-        <v>5.912937787874884</v>
+        <v>5.912937787874887</v>
       </c>
       <c r="E395">
         <v>7753038652.48</v>
       </c>
       <c r="F395">
-        <v>19.41265116178187</v>
+        <v>19.41265116178188</v>
       </c>
       <c r="G395">
         <v>14477747037.13</v>
       </c>
       <c r="H395">
-        <v>36.25049034811977</v>
+        <v>36.25049034811978</v>
       </c>
       <c r="I395">
         <v>5057585377.469999</v>
@@ -26290,7 +26392,7 @@
         <v>10288187845.44</v>
       </c>
       <c r="L395">
-        <v>25.76035160956218</v>
+        <v>25.76035160956219</v>
       </c>
       <c r="M395" s="2">
         <v>44690</v>
@@ -26313,13 +26415,13 @@
         <v>7047550639.39</v>
       </c>
       <c r="F396">
-        <v>16.45632980282691</v>
+        <v>16.45632980282692</v>
       </c>
       <c r="G396">
         <v>17687960990.38</v>
       </c>
       <c r="H396">
-        <v>41.30213949373261</v>
+        <v>41.30213949373262</v>
       </c>
       <c r="I396">
         <v>4837477994.7</v>
@@ -26348,7 +26450,7 @@
         <v>2298387215.23</v>
       </c>
       <c r="D397">
-        <v>5.606604433919998</v>
+        <v>5.606604433919999</v>
       </c>
       <c r="E397">
         <v>7080397966.540001</v>
@@ -26383,25 +26485,25 @@
         <v>411</v>
       </c>
       <c r="B398">
-        <v>35318091065.38</v>
+        <v>35318091065.37999</v>
       </c>
       <c r="C398">
         <v>1991606040.58</v>
       </c>
       <c r="D398">
-        <v>5.639053472321556</v>
+        <v>5.639053472321557</v>
       </c>
       <c r="E398">
         <v>7273763662.59</v>
       </c>
       <c r="F398">
-        <v>20.59500794967934</v>
+        <v>20.59500794967935</v>
       </c>
       <c r="G398">
         <v>12835222574.37</v>
       </c>
       <c r="H398">
-        <v>36.34177892177056</v>
+        <v>36.34177892177058</v>
       </c>
       <c r="I398">
         <v>3892980230.99</v>
@@ -26430,7 +26532,7 @@
         <v>2536302979.58</v>
       </c>
       <c r="D399">
-        <v>5.856299542477743</v>
+        <v>5.856299542477744</v>
       </c>
       <c r="E399">
         <v>8567556823.28</v>
@@ -26471,7 +26573,7 @@
         <v>2285839626.23</v>
       </c>
       <c r="D400">
-        <v>6.177272128921969</v>
+        <v>6.17727212892197</v>
       </c>
       <c r="E400">
         <v>7044975393.98</v>
@@ -26553,7 +26655,7 @@
         <v>3186488533</v>
       </c>
       <c r="D402">
-        <v>7.016881057958845</v>
+        <v>7.016881057958846</v>
       </c>
       <c r="E402">
         <v>8627315365.49</v>
@@ -26647,7 +26749,7 @@
         <v>15667952606.06</v>
       </c>
       <c r="H404">
-        <v>34.54181899197217</v>
+        <v>34.54181899197218</v>
       </c>
       <c r="I404">
         <v>6717220475.929998</v>
@@ -26676,7 +26778,7 @@
         <v>2758053693.48</v>
       </c>
       <c r="D405">
-        <v>5.778264503747367</v>
+        <v>5.778264503747369</v>
       </c>
       <c r="E405">
         <v>9306245733.910002</v>
@@ -26752,31 +26854,31 @@
         <v>420</v>
       </c>
       <c r="B407">
-        <v>48739781685.02</v>
+        <v>48739781685.01999</v>
       </c>
       <c r="C407">
         <v>2628103808.1</v>
       </c>
       <c r="D407">
-        <v>5.392112392058045</v>
+        <v>5.392112392058046</v>
       </c>
       <c r="E407">
         <v>7913040494.259999</v>
       </c>
       <c r="F407">
-        <v>16.23528095673035</v>
+        <v>16.23528095673036</v>
       </c>
       <c r="G407">
         <v>22438846307.93</v>
       </c>
       <c r="H407">
-        <v>46.03805255620688</v>
+        <v>46.03805255620689</v>
       </c>
       <c r="I407">
         <v>6875728385.139999</v>
       </c>
       <c r="J407">
-        <v>14.10701514745034</v>
+        <v>14.10701514745035</v>
       </c>
       <c r="K407">
         <v>8884062689.59</v>
@@ -26796,7 +26898,7 @@
         <v>49746227833.66</v>
       </c>
       <c r="C408">
-        <v>2432196881.929999</v>
+        <v>2432196881.93</v>
       </c>
       <c r="D408">
         <v>4.889208665353903</v>
@@ -26811,7 +26913,7 @@
         <v>26925387016.17</v>
       </c>
       <c r="H408">
-        <v>54.12548486329926</v>
+        <v>54.12548486329924</v>
       </c>
       <c r="I408">
         <v>4084151260.01</v>
@@ -26875,13 +26977,13 @@
         <v>423</v>
       </c>
       <c r="B410">
-        <v>43851539618.01</v>
+        <v>43851539618.00999</v>
       </c>
       <c r="C410">
         <v>2245382261.46</v>
       </c>
       <c r="D410">
-        <v>5.120418304623932</v>
+        <v>5.120418304623934</v>
       </c>
       <c r="E410">
         <v>7289708480.81</v>
@@ -26899,7 +27001,7 @@
         <v>3645944639.5</v>
       </c>
       <c r="J410">
-        <v>8.314291063118333</v>
+        <v>8.314291063118334</v>
       </c>
       <c r="K410">
         <v>8670937800.809999</v>
@@ -26963,7 +27065,7 @@
         <v>1609614705.08</v>
       </c>
       <c r="D412">
-        <v>5.1198907727333</v>
+        <v>5.119890772733301</v>
       </c>
       <c r="E412">
         <v>4511029497.05</v>
@@ -26981,13 +27083,13 @@
         <v>2639438637.98</v>
       </c>
       <c r="J412">
-        <v>8.395572856746428</v>
+        <v>8.39557285674643</v>
       </c>
       <c r="K412">
         <v>5653894595.08</v>
       </c>
       <c r="L412">
-        <v>17.98400740003058</v>
+        <v>17.98400740003059</v>
       </c>
       <c r="M412" s="2">
         <v>44809</v>
@@ -27086,7 +27188,7 @@
         <v>1601765253.04</v>
       </c>
       <c r="D415">
-        <v>4.252102492367174</v>
+        <v>4.252102492367173</v>
       </c>
       <c r="E415">
         <v>4371153820.059999</v>
@@ -27121,13 +27223,13 @@
         <v>429</v>
       </c>
       <c r="B416">
-        <v>39671421880.68</v>
+        <v>39671421880.67999</v>
       </c>
       <c r="C416">
         <v>1226448188.91</v>
       </c>
       <c r="D416">
-        <v>3.091515581666814</v>
+        <v>3.091515581666815</v>
       </c>
       <c r="E416">
         <v>4904339604.799999</v>
@@ -27139,7 +27241,7 @@
         <v>22160326990.77999</v>
       </c>
       <c r="H416">
-        <v>55.85967414385035</v>
+        <v>55.85967414385036</v>
       </c>
       <c r="I416">
         <v>4355097073.440001</v>
@@ -27151,7 +27253,7 @@
         <v>7025210022.75</v>
       </c>
       <c r="L416">
-        <v>17.7084906204768</v>
+        <v>17.70849062047681</v>
       </c>
       <c r="M416" s="2">
         <v>44837</v>
@@ -27162,13 +27264,13 @@
         <v>430</v>
       </c>
       <c r="B417">
-        <v>35691423164.99001</v>
+        <v>35691423164.99</v>
       </c>
       <c r="C417">
         <v>1034504672.57</v>
       </c>
       <c r="D417">
-        <v>2.898468541833752</v>
+        <v>2.898468541833754</v>
       </c>
       <c r="E417">
         <v>4282033965.72</v>
@@ -27180,19 +27282,19 @@
         <v>20187596287</v>
       </c>
       <c r="H417">
-        <v>56.56147751149966</v>
+        <v>56.56147751149967</v>
       </c>
       <c r="I417">
         <v>3788760772.44</v>
       </c>
       <c r="J417">
-        <v>10.61532557815297</v>
+        <v>10.61532557815298</v>
       </c>
       <c r="K417">
         <v>6398527467.259998</v>
       </c>
       <c r="L417">
-        <v>17.92735312817776</v>
+        <v>17.92735312817777</v>
       </c>
       <c r="M417" s="2">
         <v>44844</v>
@@ -27256,25 +27358,25 @@
         <v>3173690888.99</v>
       </c>
       <c r="F419">
-        <v>8.673119394310051</v>
+        <v>8.673119394310053</v>
       </c>
       <c r="G419">
         <v>22141030381.86</v>
       </c>
       <c r="H419">
-        <v>60.5074050157514</v>
+        <v>60.50740501575142</v>
       </c>
       <c r="I419">
         <v>3094323960.83</v>
       </c>
       <c r="J419">
-        <v>8.456224029270146</v>
+        <v>8.456224029270148</v>
       </c>
       <c r="K419">
         <v>6844722019.72</v>
       </c>
       <c r="L419">
-        <v>18.70537912303962</v>
+        <v>18.70537912303963</v>
       </c>
       <c r="M419" s="2">
         <v>44858</v>
@@ -27291,19 +27393,19 @@
         <v>1285994364.96</v>
       </c>
       <c r="D420">
-        <v>3.424871409811922</v>
+        <v>3.424871409811921</v>
       </c>
       <c r="E420">
         <v>3597201464.99</v>
       </c>
       <c r="F420">
-        <v>9.58009831805213</v>
+        <v>9.580098318052126</v>
       </c>
       <c r="G420">
         <v>21754002167.74</v>
       </c>
       <c r="H420">
-        <v>57.93544832181027</v>
+        <v>57.93544832181025</v>
       </c>
       <c r="I420">
         <v>4011518920.55</v>
@@ -27367,13 +27469,13 @@
         <v>435</v>
       </c>
       <c r="B422">
-        <v>40858212123.71999</v>
+        <v>40858212123.72</v>
       </c>
       <c r="C422">
         <v>1341591873.61</v>
       </c>
       <c r="D422">
-        <v>3.283530541051617</v>
+        <v>3.283530541051615</v>
       </c>
       <c r="E422">
         <v>4300137992.95</v>
@@ -27385,7 +27487,7 @@
         <v>20393525770.94</v>
       </c>
       <c r="H422">
-        <v>49.91291765089412</v>
+        <v>49.91291765089411</v>
       </c>
       <c r="I422">
         <v>7815450139.09</v>
@@ -27397,7 +27499,7 @@
         <v>7007506347.13</v>
       </c>
       <c r="L422">
-        <v>17.15079046021653</v>
+        <v>17.15079046021652</v>
       </c>
       <c r="M422" s="2">
         <v>44879</v>
@@ -27411,7 +27513,7 @@
         <v>29538753326.46</v>
       </c>
       <c r="C423">
-        <v>863611484.39</v>
+        <v>863611484.3899999</v>
       </c>
       <c r="D423">
         <v>2.923655832206028</v>
@@ -27426,7 +27528,7 @@
         <v>14543469831.23</v>
       </c>
       <c r="H423">
-        <v>49.23521880052521</v>
+        <v>49.2352188005252</v>
       </c>
       <c r="I423">
         <v>6804278140.200001</v>
@@ -27625,13 +27727,13 @@
         <v>2003804935.34</v>
       </c>
       <c r="F428">
-        <v>8.494767601671377</v>
+        <v>8.494767601671375</v>
       </c>
       <c r="G428">
         <v>10848534104.72</v>
       </c>
       <c r="H428">
-        <v>45.99039278379945</v>
+        <v>45.99039278379944</v>
       </c>
       <c r="I428">
         <v>5720985664.959999</v>
@@ -27643,7 +27745,7 @@
         <v>4336015867.450001</v>
       </c>
       <c r="L428">
-        <v>18.38175286502999</v>
+        <v>18.38175286502998</v>
       </c>
       <c r="M428" s="2">
         <v>44921</v>
@@ -27698,7 +27800,7 @@
         <v>32020564039.17</v>
       </c>
       <c r="C430">
-        <v>831886857.8499999</v>
+        <v>831886857.85</v>
       </c>
       <c r="D430">
         <v>2.59797690269407</v>
@@ -27713,13 +27815,13 @@
         <v>13801260297.02</v>
       </c>
       <c r="H430">
-        <v>43.10124044079063</v>
+        <v>43.10124044079062</v>
       </c>
       <c r="I430">
         <v>8352205757.700001</v>
       </c>
       <c r="J430">
-        <v>26.08388080698062</v>
+        <v>26.08388080698061</v>
       </c>
       <c r="K430">
         <v>5990013272.900002</v>
@@ -27821,10 +27923,10 @@
         <v>39423034128.31</v>
       </c>
       <c r="C433">
-        <v>984926906.73</v>
+        <v>984926906.7300001</v>
       </c>
       <c r="D433">
-        <v>2.498353890074422</v>
+        <v>2.498353890074423</v>
       </c>
       <c r="E433">
         <v>3640869444.02</v>
@@ -27859,25 +27961,25 @@
         <v>447</v>
       </c>
       <c r="B434">
-        <v>39586421595.78999</v>
+        <v>39586421595.79</v>
       </c>
       <c r="C434">
-        <v>998902375.6300001</v>
+        <v>998902375.6299999</v>
       </c>
       <c r="D434">
-        <v>2.523345974106013</v>
+        <v>2.523345974106012</v>
       </c>
       <c r="E434">
         <v>3408079134.22</v>
       </c>
       <c r="F434">
-        <v>8.609212444153952</v>
+        <v>8.60921244415395</v>
       </c>
       <c r="G434">
         <v>14094790594.47</v>
       </c>
       <c r="H434">
-        <v>35.6051141434036</v>
+        <v>35.60511414340359</v>
       </c>
       <c r="I434">
         <v>13293950246.43</v>
@@ -27944,7 +28046,7 @@
         <v>29851840416.54</v>
       </c>
       <c r="C436">
-        <v>648710280.2900001</v>
+        <v>648710280.29</v>
       </c>
       <c r="D436">
         <v>2.173099786271701</v>
@@ -27985,7 +28087,7 @@
         <v>36862948093.53</v>
       </c>
       <c r="C437">
-        <v>982056428.5899999</v>
+        <v>982056428.59</v>
       </c>
       <c r="D437">
         <v>2.664074577264659</v>
@@ -28035,7 +28137,7 @@
         <v>2699388365.99</v>
       </c>
       <c r="F438">
-        <v>7.345833857813054</v>
+        <v>7.345833857813052</v>
       </c>
       <c r="G438">
         <v>12772559979.96</v>
@@ -28053,7 +28155,7 @@
         <v>8835213880.15</v>
       </c>
       <c r="L438">
-        <v>24.04322922908609</v>
+        <v>24.04322922908608</v>
       </c>
       <c r="M438" s="2">
         <v>44991</v>
@@ -28070,31 +28172,31 @@
         <v>1087337743.3</v>
       </c>
       <c r="D439">
-        <v>2.976015860968253</v>
+        <v>2.976015860968251</v>
       </c>
       <c r="E439">
         <v>3301137284.66</v>
       </c>
       <c r="F439">
-        <v>9.035129129764135</v>
+        <v>9.035129129764133</v>
       </c>
       <c r="G439">
         <v>11785827568.72</v>
       </c>
       <c r="H439">
-        <v>32.25751151863618</v>
+        <v>32.25751151863617</v>
       </c>
       <c r="I439">
         <v>10822087445.36</v>
       </c>
       <c r="J439">
-        <v>29.61977921269566</v>
+        <v>29.61977921269565</v>
       </c>
       <c r="K439">
         <v>9540301766.66</v>
       </c>
       <c r="L439">
-        <v>26.11156427793579</v>
+        <v>26.11156427793578</v>
       </c>
       <c r="M439" s="2">
         <v>44998</v>
@@ -28111,7 +28213,7 @@
         <v>1122452577.16</v>
       </c>
       <c r="D440">
-        <v>3.015334267994511</v>
+        <v>3.015334267994512</v>
       </c>
       <c r="E440">
         <v>3394892972.55</v>
@@ -28152,25 +28254,25 @@
         <v>1000270274.4</v>
       </c>
       <c r="D441">
-        <v>2.737975989456542</v>
+        <v>2.737975989456543</v>
       </c>
       <c r="E441">
         <v>3421466753.67</v>
       </c>
       <c r="F441">
-        <v>9.365362602514105</v>
+        <v>9.365362602514107</v>
       </c>
       <c r="G441">
         <v>11366155747.51</v>
       </c>
       <c r="H441">
-        <v>31.11185279175967</v>
+        <v>31.11185279175968</v>
       </c>
       <c r="I441">
         <v>11791227571.87</v>
       </c>
       <c r="J441">
-        <v>32.27537477044717</v>
+        <v>32.27537477044719</v>
       </c>
       <c r="K441">
         <v>8954080756.279999</v>
@@ -28193,7 +28295,7 @@
         <v>766487877.4</v>
       </c>
       <c r="D442">
-        <v>2.507034194409248</v>
+        <v>2.507034194409249</v>
       </c>
       <c r="E442">
         <v>3165795478.72</v>
@@ -28205,13 +28307,13 @@
         <v>9372766127.019999</v>
       </c>
       <c r="H442">
-        <v>30.65651247655319</v>
+        <v>30.6565124765532</v>
       </c>
       <c r="I442">
         <v>9310267419.940001</v>
       </c>
       <c r="J442">
-        <v>30.45209124514713</v>
+        <v>30.45209124514714</v>
       </c>
       <c r="K442">
         <v>7958174240.73</v>
@@ -28231,28 +28333,28 @@
         <v>36942626584.02</v>
       </c>
       <c r="C443">
-        <v>913726909.3700001</v>
+        <v>913726909.37</v>
       </c>
       <c r="D443">
-        <v>2.473367472374701</v>
+        <v>2.473367472374702</v>
       </c>
       <c r="E443">
         <v>3256649150.61</v>
       </c>
       <c r="F443">
-        <v>8.815423947193578</v>
+        <v>8.81542394719358</v>
       </c>
       <c r="G443">
         <v>12040010196.03</v>
       </c>
       <c r="H443">
-        <v>32.59110493577643</v>
+        <v>32.59110493577644</v>
       </c>
       <c r="I443">
         <v>11307040126.5</v>
       </c>
       <c r="J443">
-        <v>30.60702817322416</v>
+        <v>30.60702817322417</v>
       </c>
       <c r="K443">
         <v>9425200201.51</v>
@@ -28272,10 +28374,10 @@
         <v>37460177441.33</v>
       </c>
       <c r="C444">
-        <v>898066508.5799999</v>
+        <v>898066508.58</v>
       </c>
       <c r="D444">
-        <v>2.397389894873158</v>
+        <v>2.397389894873159</v>
       </c>
       <c r="E444">
         <v>2765039260.13</v>
@@ -28313,10 +28415,10 @@
         <v>34109293565.73</v>
       </c>
       <c r="C445">
-        <v>867064495.3099999</v>
+        <v>867064495.3099998</v>
       </c>
       <c r="D445">
-        <v>2.542018331863518</v>
+        <v>2.542018331863517</v>
       </c>
       <c r="E445">
         <v>2585737208.159999</v>
@@ -28404,19 +28506,19 @@
         <v>3178870771.32</v>
       </c>
       <c r="F447">
-        <v>8.834586226977596</v>
+        <v>8.834586226977594</v>
       </c>
       <c r="G447">
         <v>13798150594.99</v>
       </c>
       <c r="H447">
-        <v>38.3472496913245</v>
+        <v>38.34724969132449</v>
       </c>
       <c r="I447">
         <v>14536407320.86</v>
       </c>
       <c r="J447">
-        <v>40.39898226289941</v>
+        <v>40.39898226289939</v>
       </c>
       <c r="K447">
         <v>3558503421.02</v>
@@ -28436,7 +28538,7 @@
         <v>36219865620.87</v>
       </c>
       <c r="C448">
-        <v>984493764.73</v>
+        <v>984493764.7299999</v>
       </c>
       <c r="D448">
         <v>2.718104409980836</v>
@@ -28556,7 +28658,7 @@
         <v>464</v>
       </c>
       <c r="B451">
-        <v>39707240883.35001</v>
+        <v>39707240883.35</v>
       </c>
       <c r="C451">
         <v>1280592232.54</v>
@@ -28574,7 +28676,7 @@
         <v>16614439573.6</v>
       </c>
       <c r="H451">
-        <v>41.84234211188103</v>
+        <v>41.84234211188104</v>
       </c>
       <c r="I451">
         <v>12363143028.99</v>
@@ -28603,7 +28705,7 @@
         <v>1611230636.13</v>
       </c>
       <c r="D452">
-        <v>3.969769850814093</v>
+        <v>3.969769850814092</v>
       </c>
       <c r="E452">
         <v>3860216336.06</v>
@@ -28644,7 +28746,7 @@
         <v>1375078776.93</v>
       </c>
       <c r="D453">
-        <v>4.341118452719826</v>
+        <v>4.341118452719827</v>
       </c>
       <c r="E453">
         <v>3494060763.8</v>
@@ -28744,13 +28846,13 @@
         <v>8850747134.41</v>
       </c>
       <c r="J455">
-        <v>27.70264693202958</v>
+        <v>27.70264693202959</v>
       </c>
       <c r="K455">
         <v>5749897567.72</v>
       </c>
       <c r="L455">
-        <v>17.99705491467541</v>
+        <v>17.99705491467542</v>
       </c>
       <c r="M455" s="2">
         <v>45110</v>
@@ -28764,10 +28866,10 @@
         <v>42660756661.93</v>
       </c>
       <c r="C456">
-        <v>1873128693.82</v>
+        <v>1873128693.819999</v>
       </c>
       <c r="D456">
-        <v>4.390753564602289</v>
+        <v>4.390753564602288</v>
       </c>
       <c r="E456">
         <v>4279371531.67</v>
@@ -28808,7 +28910,7 @@
         <v>2069773530.78</v>
       </c>
       <c r="D457">
-        <v>4.540106463658979</v>
+        <v>4.540106463658978</v>
       </c>
       <c r="E457">
         <v>4414847990.83</v>
@@ -28843,7 +28945,7 @@
         <v>471</v>
       </c>
       <c r="B458">
-        <v>43665933760.93</v>
+        <v>43665933760.93001</v>
       </c>
       <c r="C458">
         <v>1765565134.78</v>
@@ -28861,19 +28963,19 @@
         <v>17492913004.2</v>
       </c>
       <c r="H458">
-        <v>40.06077850063463</v>
+        <v>40.06077850063461</v>
       </c>
       <c r="I458">
         <v>10768306756.22</v>
       </c>
       <c r="J458">
-        <v>24.66065838687027</v>
+        <v>24.66065838687026</v>
       </c>
       <c r="K458">
         <v>8987518221.65</v>
       </c>
       <c r="L458">
-        <v>20.58244825555881</v>
+        <v>20.5824482555588</v>
       </c>
       <c r="M458" s="2">
         <v>45131</v>
@@ -28890,7 +28992,7 @@
         <v>1776187977.71</v>
       </c>
       <c r="D459">
-        <v>4.031664620178528</v>
+        <v>4.031664620178529</v>
       </c>
       <c r="E459">
         <v>4521466658.87</v>
@@ -28925,7 +29027,7 @@
         <v>473</v>
       </c>
       <c r="B460">
-        <v>39952515359.1</v>
+        <v>39952515359.10001</v>
       </c>
       <c r="C460">
         <v>1284504756.85</v>
@@ -28943,19 +29045,19 @@
         <v>15697674152.17</v>
       </c>
       <c r="H460">
-        <v>39.2908281520616</v>
+        <v>39.29082815206159</v>
       </c>
       <c r="I460">
         <v>7346834935.33</v>
       </c>
       <c r="J460">
-        <v>18.38891711647039</v>
+        <v>18.38891711647038</v>
       </c>
       <c r="K460">
         <v>10990999080.98</v>
       </c>
       <c r="L460">
-        <v>27.5101554487647</v>
+        <v>27.51015544876469</v>
       </c>
       <c r="M460" s="2">
         <v>45145</v>
@@ -29007,25 +29109,25 @@
         <v>475</v>
       </c>
       <c r="B462">
-        <v>37040727552.22</v>
+        <v>37040727552.21999</v>
       </c>
       <c r="C462">
         <v>1539099187.19</v>
       </c>
       <c r="D462">
-        <v>4.155153769644991</v>
+        <v>4.155153769644992</v>
       </c>
       <c r="E462">
         <v>3271278506.22</v>
       </c>
       <c r="F462">
-        <v>8.831571954433542</v>
+        <v>8.831571954433546</v>
       </c>
       <c r="G462">
         <v>15372006964.4</v>
       </c>
       <c r="H462">
-        <v>41.50028355336312</v>
+        <v>41.50028355336313</v>
       </c>
       <c r="I462">
         <v>5351846007.96</v>
@@ -29037,7 +29139,7 @@
         <v>11506496886.45</v>
       </c>
       <c r="L462">
-        <v>31.06444621053445</v>
+        <v>31.06444621053446</v>
       </c>
       <c r="M462" s="2">
         <v>45159</v>
@@ -29107,7 +29209,7 @@
         <v>12825235490.85</v>
       </c>
       <c r="H464">
-        <v>40.90194813913927</v>
+        <v>40.90194813913926</v>
       </c>
       <c r="I464">
         <v>5285882934.799999</v>
@@ -29265,7 +29367,7 @@
         <v>2860886955.53</v>
       </c>
       <c r="F468">
-        <v>8.552349151717957</v>
+        <v>8.552349151717959</v>
       </c>
       <c r="G468">
         <v>15067865612.35</v>
@@ -29277,13 +29379,13 @@
         <v>2294582850.44</v>
       </c>
       <c r="J468">
-        <v>6.859436950689163</v>
+        <v>6.859436950689164</v>
       </c>
       <c r="K468">
         <v>11764311803.16</v>
       </c>
       <c r="L468">
-        <v>35.16828998636955</v>
+        <v>35.16828998636956</v>
       </c>
       <c r="M468" s="2">
         <v>45201</v>
@@ -29338,7 +29440,7 @@
         <v>32786553664.16</v>
       </c>
       <c r="C470">
-        <v>923458329.13</v>
+        <v>923458329.1300001</v>
       </c>
       <c r="D470">
         <v>2.816576388568284</v>
@@ -29420,7 +29522,7 @@
         <v>30540071251.35</v>
       </c>
       <c r="C472">
-        <v>948120101.5700001</v>
+        <v>948120101.5699999</v>
       </c>
       <c r="D472">
         <v>3.104511753645922</v>
@@ -29435,7 +29537,7 @@
         <v>12485577143.87</v>
       </c>
       <c r="H472">
-        <v>40.88260646516364</v>
+        <v>40.88260646516365</v>
       </c>
       <c r="I472">
         <v>4182409998.64</v>
@@ -29499,7 +29601,7 @@
         <v>487</v>
       </c>
       <c r="B474">
-        <v>36577796559.76999</v>
+        <v>36577796559.77</v>
       </c>
       <c r="C474">
         <v>1555246510.93</v>
@@ -29517,7 +29619,7 @@
         <v>13423573570.62</v>
       </c>
       <c r="H474">
-        <v>36.69869383379939</v>
+        <v>36.69869383379938</v>
       </c>
       <c r="I474">
         <v>7218923521.939999</v>
@@ -29529,7 +29631,7 @@
         <v>9705698315.529999</v>
       </c>
       <c r="L474">
-        <v>26.53439853784083</v>
+        <v>26.53439853784082</v>
       </c>
       <c r="M474" s="2">
         <v>45243</v>
@@ -29552,25 +29654,25 @@
         <v>5580616179.710001</v>
       </c>
       <c r="F475">
-        <v>17.78236628724835</v>
+        <v>17.78236628724836</v>
       </c>
       <c r="G475">
         <v>9880456703.870001</v>
       </c>
       <c r="H475">
-        <v>31.48360226462396</v>
+        <v>31.48360226462397</v>
       </c>
       <c r="I475">
         <v>6480306526.09</v>
       </c>
       <c r="J475">
-        <v>20.64918650373238</v>
+        <v>20.64918650373239</v>
       </c>
       <c r="K475">
         <v>8347835018.6</v>
       </c>
       <c r="L475">
-        <v>26.59997663805968</v>
+        <v>26.59997663805969</v>
       </c>
       <c r="M475" s="2">
         <v>45250</v>
@@ -29581,13 +29683,13 @@
         <v>489</v>
       </c>
       <c r="B476">
-        <v>40428669914.53999</v>
+        <v>40428669914.54</v>
       </c>
       <c r="C476">
         <v>1413415678.43</v>
       </c>
       <c r="D476">
-        <v>3.496072666792511</v>
+        <v>3.49607266679251</v>
       </c>
       <c r="E476">
         <v>7764708705.950001</v>
@@ -29599,7 +29701,7 @@
         <v>12087152777.28</v>
       </c>
       <c r="H476">
-        <v>29.89747820749579</v>
+        <v>29.89747820749578</v>
       </c>
       <c r="I476">
         <v>7872652437.75</v>
@@ -29611,7 +29713,7 @@
         <v>11290740315.13</v>
       </c>
       <c r="L476">
-        <v>27.92755818827801</v>
+        <v>27.927558188278</v>
       </c>
       <c r="M476" s="2">
         <v>45257</v>
@@ -29622,7 +29724,7 @@
         <v>490</v>
       </c>
       <c r="B477">
-        <v>41576401327.40001</v>
+        <v>41576401327.4</v>
       </c>
       <c r="C477">
         <v>1575107531.43</v>
@@ -29652,7 +29754,7 @@
         <v>13415939907.66</v>
       </c>
       <c r="L477">
-        <v>32.26816049329051</v>
+        <v>32.26816049329052</v>
       </c>
       <c r="M477" s="2">
         <v>45264</v>
@@ -29669,7 +29771,7 @@
         <v>1493613920.47</v>
       </c>
       <c r="D478">
-        <v>3.456427393288666</v>
+        <v>3.456427393288664</v>
       </c>
       <c r="E478">
         <v>8075848351.349999</v>
@@ -29751,7 +29853,7 @@
         <v>1491802348.65</v>
       </c>
       <c r="D480">
-        <v>3.894856241674303</v>
+        <v>3.894856241674302</v>
       </c>
       <c r="E480">
         <v>7438417882.649999</v>
@@ -29845,7 +29947,7 @@
         <v>14089582077.49</v>
       </c>
       <c r="H482">
-        <v>33.03974610685923</v>
+        <v>33.03974610685924</v>
       </c>
       <c r="I482">
         <v>10933373663.15</v>
@@ -29886,13 +29988,13 @@
         <v>10969841623.8</v>
       </c>
       <c r="H483">
-        <v>34.74661908898504</v>
+        <v>34.74661908898503</v>
       </c>
       <c r="I483">
         <v>8657502155.639999</v>
       </c>
       <c r="J483">
-        <v>27.42235849708512</v>
+        <v>27.42235849708511</v>
       </c>
       <c r="K483">
         <v>5366635820.73</v>
@@ -29909,7 +30011,7 @@
         <v>497</v>
       </c>
       <c r="B484">
-        <v>39323041904.24001</v>
+        <v>39323041904.24</v>
       </c>
       <c r="C484">
         <v>1397806058.7</v>
@@ -29921,7 +30023,7 @@
         <v>7896456445.05</v>
       </c>
       <c r="F484">
-        <v>20.08099084572235</v>
+        <v>20.08099084572236</v>
       </c>
       <c r="G484">
         <v>12380678293.89</v>
@@ -29933,7 +30035,7 @@
         <v>8864626012.619999</v>
       </c>
       <c r="J484">
-        <v>22.5430830966924</v>
+        <v>22.54308309669241</v>
       </c>
       <c r="K484">
         <v>8783475093.980001</v>
@@ -29997,7 +30099,7 @@
         <v>1002173341.01</v>
       </c>
       <c r="D486">
-        <v>2.58272970677711</v>
+        <v>2.582729706777111</v>
       </c>
       <c r="E486">
         <v>7983018149.27</v>
@@ -30038,7 +30140,7 @@
         <v>1112237535.47</v>
       </c>
       <c r="D487">
-        <v>2.70331690449898</v>
+        <v>2.703316904498981</v>
       </c>
       <c r="E487">
         <v>8710497904.780001</v>
@@ -30076,16 +30178,16 @@
         <v>31443130079.13</v>
       </c>
       <c r="C488">
-        <v>847498179.0699999</v>
+        <v>847498179.0700001</v>
       </c>
       <c r="D488">
-        <v>2.695336555035011</v>
+        <v>2.695336555035012</v>
       </c>
       <c r="E488">
         <v>7499695152.839999</v>
       </c>
       <c r="F488">
-        <v>23.85161761556885</v>
+        <v>23.85161761556886</v>
       </c>
       <c r="G488">
         <v>9484559329.07</v>
@@ -30097,7 +30199,7 @@
         <v>7916124556.219999</v>
       </c>
       <c r="J488">
-        <v>25.17600676617825</v>
+        <v>25.17600676617826</v>
       </c>
       <c r="K488">
         <v>5695252861.93</v>
@@ -30155,13 +30257,13 @@
         <v>503</v>
       </c>
       <c r="B490">
-        <v>39639155885.20999</v>
+        <v>39639155885.21</v>
       </c>
       <c r="C490">
         <v>1202431832.81</v>
       </c>
       <c r="D490">
-        <v>3.033444597791364</v>
+        <v>3.033444597791363</v>
       </c>
       <c r="E490">
         <v>8694248845.459999</v>
@@ -30185,7 +30287,7 @@
         <v>7534955859.53</v>
       </c>
       <c r="L490">
-        <v>19.00887062618156</v>
+        <v>19.00887062618155</v>
       </c>
       <c r="M490" s="2">
         <v>45355</v>
@@ -30196,37 +30298,37 @@
         <v>504</v>
       </c>
       <c r="B491">
-        <v>31316735250.53001</v>
+        <v>31300428802.54</v>
       </c>
       <c r="C491">
         <v>1065491524.64</v>
       </c>
       <c r="D491">
-        <v>3.402307156592792</v>
+        <v>3.404079641725343</v>
       </c>
       <c r="E491">
         <v>6785069253.379999</v>
       </c>
       <c r="F491">
-        <v>21.66595336040071</v>
+        <v>21.67724057770543</v>
       </c>
       <c r="G491">
         <v>9482588205.219999</v>
       </c>
       <c r="H491">
-        <v>30.27961928138571</v>
+        <v>30.29539392268804</v>
       </c>
       <c r="I491">
         <v>8164366169.57</v>
       </c>
       <c r="J491">
-        <v>26.07029789106713</v>
+        <v>26.08387962054842</v>
       </c>
       <c r="K491">
         <v>5802913649.73</v>
       </c>
       <c r="L491">
-        <v>18.52975287272893</v>
+        <v>18.53940623733276</v>
       </c>
       <c r="M491" s="2">
         <v>45362</v>
@@ -30243,7 +30345,7 @@
         <v>1789981675.9</v>
       </c>
       <c r="D492">
-        <v>4.67514339150894</v>
+        <v>4.675143391508939</v>
       </c>
       <c r="E492">
         <v>7763660153</v>
@@ -30284,7 +30386,7 @@
         <v>1318747964.59</v>
       </c>
       <c r="D493">
-        <v>4.227284202698108</v>
+        <v>4.227284202698107</v>
       </c>
       <c r="E493">
         <v>7487072096.98</v>
@@ -30407,19 +30509,19 @@
         <v>911971209.99</v>
       </c>
       <c r="D496">
-        <v>2.75243150555961</v>
+        <v>2.752431505559611</v>
       </c>
       <c r="E496">
         <v>8681942764.120001</v>
       </c>
       <c r="F496">
-        <v>26.20307804858358</v>
+        <v>26.20307804858359</v>
       </c>
       <c r="G496">
         <v>10141152696.69</v>
       </c>
       <c r="H496">
-        <v>30.60713746146266</v>
+        <v>30.60713746146267</v>
       </c>
       <c r="I496">
         <v>4514424169.530001</v>
@@ -30431,7 +30533,7 @@
         <v>8883802691.15</v>
       </c>
       <c r="L496">
-        <v>26.81231397267972</v>
+        <v>26.81231397267973</v>
       </c>
       <c r="M496" s="2">
         <v>45397</v>
@@ -30466,13 +30568,13 @@
         <v>4088259876.55</v>
       </c>
       <c r="J497">
-        <v>12.67033118604791</v>
+        <v>12.67033118604792</v>
       </c>
       <c r="K497">
         <v>8931757261.869999</v>
       </c>
       <c r="L497">
-        <v>27.68129375297488</v>
+        <v>27.68129375297489</v>
       </c>
       <c r="M497" s="2">
         <v>45404</v>
@@ -30524,25 +30626,25 @@
         <v>512</v>
       </c>
       <c r="B499">
-        <v>33255595256.10999</v>
+        <v>33255595256.11</v>
       </c>
       <c r="C499">
         <v>1088617231.07</v>
       </c>
       <c r="D499">
-        <v>3.273485928266433</v>
+        <v>3.273485928266432</v>
       </c>
       <c r="E499">
         <v>8389661848.25</v>
       </c>
       <c r="F499">
-        <v>25.22782041229162</v>
+        <v>25.22782041229161</v>
       </c>
       <c r="G499">
         <v>10081741623.89</v>
       </c>
       <c r="H499">
-        <v>30.31592592539056</v>
+        <v>30.31592592539055</v>
       </c>
       <c r="I499">
         <v>4323425697.92</v>
@@ -30609,7 +30711,7 @@
         <v>32754775866.32</v>
       </c>
       <c r="C501">
-        <v>980057027.4499999</v>
+        <v>980057027.45</v>
       </c>
       <c r="D501">
         <v>2.99210420932155</v>
@@ -30691,7 +30793,7 @@
         <v>31284481529.19</v>
       </c>
       <c r="C503">
-        <v>980705765.0999999</v>
+        <v>980705765.1</v>
       </c>
       <c r="D503">
         <v>3.134799482564389</v>
@@ -30706,7 +30808,7 @@
         <v>7068346015.889999</v>
       </c>
       <c r="H503">
-        <v>22.59377707536842</v>
+        <v>22.59377707536843</v>
       </c>
       <c r="I503">
         <v>5150872558.490001</v>
@@ -30776,7 +30878,7 @@
         <v>1076778944.82</v>
       </c>
       <c r="D505">
-        <v>4.347550668012221</v>
+        <v>4.347550668012222</v>
       </c>
       <c r="E505">
         <v>5354900711.39</v>
@@ -30817,7 +30919,7 @@
         <v>1324841107.57</v>
       </c>
       <c r="D506">
-        <v>4.423513433962928</v>
+        <v>4.423513433962929</v>
       </c>
       <c r="E506">
         <v>7023393463.45</v>
@@ -30858,13 +30960,13 @@
         <v>1026713413.18</v>
       </c>
       <c r="D507">
-        <v>4.192355235802686</v>
+        <v>4.192355235802687</v>
       </c>
       <c r="E507">
         <v>6027166825.849998</v>
       </c>
       <c r="F507">
-        <v>24.61059150006311</v>
+        <v>24.61059150006312</v>
       </c>
       <c r="G507">
         <v>6811969039.35</v>
@@ -30940,13 +31042,13 @@
         <v>988958998.4400001</v>
       </c>
       <c r="D509">
-        <v>3.007152600134813</v>
+        <v>3.007152600134812</v>
       </c>
       <c r="E509">
         <v>7987697176.05</v>
       </c>
       <c r="F509">
-        <v>24.28839251165938</v>
+        <v>24.28839251165937</v>
       </c>
       <c r="G509">
         <v>9138313160.65</v>
@@ -31019,10 +31121,10 @@
         <v>29565501625.09</v>
       </c>
       <c r="C511">
-        <v>818856869.1200001</v>
+        <v>818856869.1199999</v>
       </c>
       <c r="D511">
-        <v>2.769636312969229</v>
+        <v>2.769636312969228</v>
       </c>
       <c r="E511">
         <v>5942858068.739999</v>
@@ -31034,7 +31136,7 @@
         <v>8681379321.889999</v>
       </c>
       <c r="H511">
-        <v>29.36320659116696</v>
+        <v>29.36320659116695</v>
       </c>
       <c r="I511">
         <v>4837397979.000001</v>
@@ -31110,13 +31212,13 @@
         <v>6706374782.48</v>
       </c>
       <c r="F513">
-        <v>24.82328158186201</v>
+        <v>24.823281581862</v>
       </c>
       <c r="G513">
         <v>8013358000.560001</v>
       </c>
       <c r="H513">
-        <v>29.66100889318452</v>
+        <v>29.66100889318451</v>
       </c>
       <c r="I513">
         <v>3068713929.67</v>
@@ -31128,7 +31230,7 @@
         <v>8426500814.310001</v>
       </c>
       <c r="L513">
-        <v>31.19023455263186</v>
+        <v>31.19023455263185</v>
       </c>
       <c r="M513" s="2">
         <v>45516</v>
@@ -31186,7 +31288,7 @@
         <v>1201745991.78</v>
       </c>
       <c r="D515">
-        <v>4.158002568382541</v>
+        <v>4.158002568382542</v>
       </c>
       <c r="E515">
         <v>6743107873.08</v>
@@ -31227,7 +31329,7 @@
         <v>1142129408.09</v>
       </c>
       <c r="D516">
-        <v>5.255218856642466</v>
+        <v>5.255218856642465</v>
       </c>
       <c r="E516">
         <v>4717316017.670001</v>
@@ -31268,13 +31370,13 @@
         <v>1066568511.01</v>
       </c>
       <c r="D517">
-        <v>3.975623609737042</v>
+        <v>3.975623609737041</v>
       </c>
       <c r="E517">
         <v>6274265598.63</v>
       </c>
       <c r="F517">
-        <v>23.3872631623572</v>
+        <v>23.38726316235719</v>
       </c>
       <c r="G517">
         <v>8508822678.220001</v>
@@ -31315,7 +31417,7 @@
         <v>7343211065.76</v>
       </c>
       <c r="F518">
-        <v>25.47544448238563</v>
+        <v>25.47544448238562</v>
       </c>
       <c r="G518">
         <v>8325597359.63</v>
@@ -31350,7 +31452,7 @@
         <v>1093717565.87</v>
       </c>
       <c r="D519">
-        <v>3.798878891892646</v>
+        <v>3.798878891892645</v>
       </c>
       <c r="E519">
         <v>7218544364.57</v>
@@ -31491,7 +31593,7 @@
         <v>5024195549.959999</v>
       </c>
       <c r="J522">
-        <v>17.94550924513411</v>
+        <v>17.94550924513412</v>
       </c>
       <c r="K522">
         <v>8536829281.72</v>
@@ -31514,13 +31616,13 @@
         <v>1024358750.04</v>
       </c>
       <c r="D523">
-        <v>3.68026803751293</v>
+        <v>3.680268037512929</v>
       </c>
       <c r="E523">
         <v>7714728742.2</v>
       </c>
       <c r="F523">
-        <v>27.71711532399396</v>
+        <v>27.71711532399395</v>
       </c>
       <c r="G523">
         <v>5397323573.930001</v>
@@ -31532,13 +31634,13 @@
         <v>4639438051.63</v>
       </c>
       <c r="J523">
-        <v>16.6683552737441</v>
+        <v>16.66835527374409</v>
       </c>
       <c r="K523">
         <v>9057959170.040001</v>
       </c>
       <c r="L523">
-        <v>32.54301055884341</v>
+        <v>32.5430105588434</v>
       </c>
       <c r="M523" s="2">
         <v>45586</v>
@@ -31552,7 +31654,7 @@
         <v>28508658437.35</v>
       </c>
       <c r="C524">
-        <v>900852487.9699999</v>
+        <v>900852487.97</v>
       </c>
       <c r="D524">
         <v>3.159925921978032</v>
@@ -31643,7 +31745,7 @@
         <v>9780076382.630001</v>
       </c>
       <c r="F526">
-        <v>29.56046114066683</v>
+        <v>29.56046114066682</v>
       </c>
       <c r="G526">
         <v>6791613765.719999</v>
@@ -31661,7 +31763,7 @@
         <v>11230178622.81</v>
       </c>
       <c r="L526">
-        <v>33.94342189105185</v>
+        <v>33.94342189105184</v>
       </c>
       <c r="M526" s="2">
         <v>45607</v>
@@ -31839,10 +31941,10 @@
         <v>34374170885.61</v>
       </c>
       <c r="C531">
-        <v>797943769.1500001</v>
+        <v>797943769.1499999</v>
       </c>
       <c r="D531">
-        <v>2.32134695497206</v>
+        <v>2.321346954972059</v>
       </c>
       <c r="E531">
         <v>10746719181.79</v>
@@ -31921,7 +32023,7 @@
         <v>25454089256.15</v>
       </c>
       <c r="C533">
-        <v>592518232.41</v>
+        <v>592518232.4100001</v>
       </c>
       <c r="D533">
         <v>2.327791917626127</v>
@@ -31930,7 +32032,7 @@
         <v>8268121254.83</v>
       </c>
       <c r="F533">
-        <v>32.4824870834156</v>
+        <v>32.48248708341559</v>
       </c>
       <c r="G533">
         <v>5282654478.959999</v>
@@ -31942,13 +32044,13 @@
         <v>3074086132.4</v>
       </c>
       <c r="J533">
-        <v>12.07698339337467</v>
+        <v>12.07698339337466</v>
       </c>
       <c r="K533">
         <v>8236709157.550001</v>
       </c>
       <c r="L533">
-        <v>32.35908020382194</v>
+        <v>32.35908020382193</v>
       </c>
       <c r="M533" s="2">
         <v>45656</v>
@@ -32208,7 +32310,7 @@
         <v>28286813945.88</v>
       </c>
       <c r="C540">
-        <v>739760230.5999999</v>
+        <v>739760230.6</v>
       </c>
       <c r="D540">
         <v>2.61521227528612</v>
@@ -32217,7 +32319,7 @@
         <v>8481448927.860001</v>
       </c>
       <c r="F540">
-        <v>29.98375477735742</v>
+        <v>29.98375477735743</v>
       </c>
       <c r="G540">
         <v>5731317343.190001</v>
@@ -32235,7 +32337,7 @@
         <v>6173298305.45</v>
       </c>
       <c r="L540">
-        <v>21.82394354224946</v>
+        <v>21.82394354224947</v>
       </c>
       <c r="M540" s="2">
         <v>45705</v>
@@ -32249,7 +32351,7 @@
         <v>30668648928.63</v>
       </c>
       <c r="C541">
-        <v>833330672.8499999</v>
+        <v>833330672.85</v>
       </c>
       <c r="D541">
         <v>2.717206991378298</v>
@@ -32358,7 +32460,7 @@
         <v>5514853477.139999</v>
       </c>
       <c r="L543">
-        <v>20.4847985862312</v>
+        <v>20.48479858623119</v>
       </c>
       <c r="M543" s="2">
         <v>45726</v>
@@ -32372,7 +32474,7 @@
         <v>26775294784.1</v>
       </c>
       <c r="C544">
-        <v>531375979.9199999</v>
+        <v>531375979.92</v>
       </c>
       <c r="D544">
         <v>1.984575647830206</v>
@@ -32381,13 +32483,13 @@
         <v>7733583779.51</v>
       </c>
       <c r="F544">
-        <v>28.88328155439186</v>
+        <v>28.88328155439185</v>
       </c>
       <c r="G544">
         <v>6590818664.27</v>
       </c>
       <c r="H544">
-        <v>24.61529823448978</v>
+        <v>24.61529823448977</v>
       </c>
       <c r="I544">
         <v>6956576094.150001</v>
@@ -32434,7 +32536,7 @@
         <v>8392152987.75</v>
       </c>
       <c r="J545">
-        <v>29.83827602527987</v>
+        <v>29.83827602527988</v>
       </c>
       <c r="K545">
         <v>5606558904.57</v>
@@ -32469,7 +32571,7 @@
         <v>5419888903.830002</v>
       </c>
       <c r="H546">
-        <v>21.68430292607088</v>
+        <v>21.68430292607087</v>
       </c>
       <c r="I546">
         <v>5812389266.47</v>
@@ -32539,13 +32641,13 @@
         <v>389495330.76</v>
       </c>
       <c r="D548">
-        <v>1.943164325415793</v>
+        <v>1.943164325415794</v>
       </c>
       <c r="E548">
         <v>6175977334.349999</v>
       </c>
       <c r="F548">
-        <v>30.81150884984602</v>
+        <v>30.81150884984603</v>
       </c>
       <c r="G548">
         <v>4089561468.3</v>
@@ -32580,13 +32682,13 @@
         <v>574157526.0600001</v>
       </c>
       <c r="D549">
-        <v>2.348565214524542</v>
+        <v>2.348565214524543</v>
       </c>
       <c r="E549">
         <v>7095915156.13</v>
       </c>
       <c r="F549">
-        <v>29.02551781436175</v>
+        <v>29.02551781436176</v>
       </c>
       <c r="G549">
         <v>4679547150.02</v>
@@ -32604,7 +32706,7 @@
         <v>7290337427.34</v>
       </c>
       <c r="L549">
-        <v>29.82079326119957</v>
+        <v>29.82079326119958</v>
       </c>
       <c r="M549" s="2">
         <v>45768</v>
@@ -32618,10 +32720,10 @@
         <v>25964750676.56</v>
       </c>
       <c r="C550">
-        <v>706102692.5400001</v>
+        <v>706102692.5399998</v>
       </c>
       <c r="D550">
-        <v>2.719466484911958</v>
+        <v>2.719466484911957</v>
       </c>
       <c r="E550">
         <v>7794929649.320001</v>
@@ -32659,7 +32761,7 @@
         <v>25614645443.08</v>
       </c>
       <c r="C551">
-        <v>889470222.3300002</v>
+        <v>889470222.33</v>
       </c>
       <c r="D551">
         <v>3.472506478009039</v>
@@ -32674,13 +32776,13 @@
         <v>4193171260.63</v>
       </c>
       <c r="H551">
-        <v>16.3702100423288</v>
+        <v>16.37021004232881</v>
       </c>
       <c r="I551">
         <v>4550064257.57</v>
       </c>
       <c r="J551">
-        <v>17.76352621269343</v>
+        <v>17.76352621269344</v>
       </c>
       <c r="K551">
         <v>7938199514.679999</v>
@@ -32744,7 +32846,7 @@
         <v>1320829584.54</v>
       </c>
       <c r="D553">
-        <v>4.623652935727512</v>
+        <v>4.623652935727513</v>
       </c>
       <c r="E553">
         <v>8467850906.91</v>
@@ -32867,7 +32969,7 @@
         <v>1831052827.73</v>
       </c>
       <c r="D556">
-        <v>5.923975521857026</v>
+        <v>5.923975521857025</v>
       </c>
       <c r="E556">
         <v>8719821646.779999</v>
@@ -32908,7 +33010,7 @@
         <v>1341937164.67</v>
       </c>
       <c r="D557">
-        <v>5.461014812463624</v>
+        <v>5.461014812463626</v>
       </c>
       <c r="E557">
         <v>6843621451.9</v>
@@ -32949,7 +33051,7 @@
         <v>2240674106.96</v>
       </c>
       <c r="D558">
-        <v>6.750472315835314</v>
+        <v>6.750472315835315</v>
       </c>
       <c r="E558">
         <v>8521363839.650001</v>
@@ -32961,7 +33063,7 @@
         <v>7592531218.68</v>
       </c>
       <c r="H558">
-        <v>22.87399655291757</v>
+        <v>22.87399655291758</v>
       </c>
       <c r="I558">
         <v>8459114124.39</v>
@@ -32990,7 +33092,7 @@
         <v>1925311106.53</v>
       </c>
       <c r="D559">
-        <v>7.135096000610873</v>
+        <v>7.13509600061087</v>
       </c>
       <c r="E559">
         <v>7142029979.919999</v>
@@ -33014,7 +33116,7 @@
         <v>6435136996.91</v>
       </c>
       <c r="L559">
-        <v>23.8482602080809</v>
+        <v>23.84826020808089</v>
       </c>
       <c r="M559" s="2">
         <v>45838</v>
@@ -33031,7 +33133,7 @@
         <v>2333346244.48</v>
       </c>
       <c r="D560">
-        <v>6.753549977306769</v>
+        <v>6.753549977306768</v>
       </c>
       <c r="E560">
         <v>9340566096.059998</v>
@@ -33113,7 +33215,7 @@
         <v>3258669433.03</v>
       </c>
       <c r="D562">
-        <v>8.823626570372548</v>
+        <v>8.82362657037255</v>
       </c>
       <c r="E562">
         <v>9277892959.459999</v>
@@ -33154,7 +33256,7 @@
         <v>3249140653.68</v>
       </c>
       <c r="D563">
-        <v>8.730644249954645</v>
+        <v>8.730644249954647</v>
       </c>
       <c r="E563">
         <v>10415201813.73</v>
@@ -33201,19 +33303,19 @@
         <v>10570330922.39</v>
       </c>
       <c r="F564">
-        <v>30.33223201742445</v>
+        <v>30.33223201742446</v>
       </c>
       <c r="G564">
         <v>7371141628.19</v>
       </c>
       <c r="H564">
-        <v>21.15195633335968</v>
+        <v>21.15195633335969</v>
       </c>
       <c r="I564">
         <v>10856022448.84</v>
       </c>
       <c r="J564">
-        <v>31.15204189180956</v>
+        <v>31.15204189180957</v>
       </c>
       <c r="K564">
         <v>3559003682.559999</v>
@@ -33233,10 +33335,10 @@
         <v>48508893675.29</v>
       </c>
       <c r="C565">
-        <v>2992446024.190001</v>
+        <v>2992446024.19</v>
       </c>
       <c r="D565">
-        <v>6.168860589196092</v>
+        <v>6.168860589196091</v>
       </c>
       <c r="E565">
         <v>14085624299.03</v>
@@ -33271,13 +33373,13 @@
         <v>579</v>
       </c>
       <c r="B566">
-        <v>39231797979.35999</v>
+        <v>39231797979.36</v>
       </c>
       <c r="C566">
         <v>2017812640.65</v>
       </c>
       <c r="D566">
-        <v>5.143309112958778</v>
+        <v>5.143309112958776</v>
       </c>
       <c r="E566">
         <v>12504303810.17</v>
@@ -33289,7 +33391,7 @@
         <v>10216452165.37</v>
       </c>
       <c r="H566">
-        <v>26.04125401222987</v>
+        <v>26.04125401222986</v>
       </c>
       <c r="I566">
         <v>10418258028.29</v>
@@ -33312,40 +33414,286 @@
         <v>580</v>
       </c>
       <c r="B567">
-        <v>22623430018.15</v>
+        <v>37292528638.39999</v>
       </c>
       <c r="C567">
-        <v>1071470657.28</v>
+        <v>1772300714.86</v>
       </c>
       <c r="D567">
-        <v>4.736110556270185</v>
+        <v>4.752428380614201</v>
       </c>
       <c r="E567">
-        <v>7369925503.280001</v>
+        <v>12183722387.56</v>
       </c>
       <c r="F567">
-        <v>32.57651690025501</v>
+        <v>32.67067917463355</v>
       </c>
       <c r="G567">
-        <v>5499127346.98</v>
+        <v>8796608514.189999</v>
       </c>
       <c r="H567">
-        <v>24.30722194896282</v>
+        <v>23.58812565241865</v>
       </c>
       <c r="I567">
-        <v>6218175248.55</v>
+        <v>10461719144.87</v>
       </c>
       <c r="J567">
-        <v>27.48555477025974</v>
+        <v>28.05312357955154</v>
       </c>
       <c r="K567">
-        <v>2464731262.06</v>
+        <v>4078177876.92</v>
       </c>
       <c r="L567">
-        <v>10.89459582425225</v>
+        <v>10.93564321278207</v>
       </c>
       <c r="M567" s="2">
         <v>45894</v>
+      </c>
+    </row>
+    <row r="568" spans="1:13">
+      <c r="A568" t="s">
+        <v>581</v>
+      </c>
+      <c r="B568">
+        <v>28487447469.48</v>
+      </c>
+      <c r="C568">
+        <v>1429239713.13</v>
+      </c>
+      <c r="D568">
+        <v>5.017085910070444</v>
+      </c>
+      <c r="E568">
+        <v>9442559674.280001</v>
+      </c>
+      <c r="F568">
+        <v>33.14638731461033</v>
+      </c>
+      <c r="G568">
+        <v>6154197563.929998</v>
+      </c>
+      <c r="H568">
+        <v>21.60319056497881</v>
+      </c>
+      <c r="I568">
+        <v>8413255194.610001</v>
+      </c>
+      <c r="J568">
+        <v>29.53320125863693</v>
+      </c>
+      <c r="K568">
+        <v>3048195323.53</v>
+      </c>
+      <c r="L568">
+        <v>10.70013495170349</v>
+      </c>
+      <c r="M568" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="569" spans="1:13">
+      <c r="A569" t="s">
+        <v>582</v>
+      </c>
+      <c r="B569">
+        <v>44468831947.31</v>
+      </c>
+      <c r="C569">
+        <v>2493392997.49</v>
+      </c>
+      <c r="D569">
+        <v>5.607057546382956</v>
+      </c>
+      <c r="E569">
+        <v>13914231789.03</v>
+      </c>
+      <c r="F569">
+        <v>31.28985219471612</v>
+      </c>
+      <c r="G569">
+        <v>10069116883.95</v>
+      </c>
+      <c r="H569">
+        <v>22.6430883003193</v>
+      </c>
+      <c r="I569">
+        <v>13068487978.47</v>
+      </c>
+      <c r="J569">
+        <v>29.38797221828206</v>
+      </c>
+      <c r="K569">
+        <v>4923602298.37</v>
+      </c>
+      <c r="L569">
+        <v>11.07202974029957</v>
+      </c>
+      <c r="M569" s="2">
+        <v>45908</v>
+      </c>
+    </row>
+    <row r="570" spans="1:13">
+      <c r="A570" t="s">
+        <v>583</v>
+      </c>
+      <c r="B570">
+        <v>45111555471.73</v>
+      </c>
+      <c r="C570">
+        <v>3088950230.19</v>
+      </c>
+      <c r="D570">
+        <v>6.847359169704863</v>
+      </c>
+      <c r="E570">
+        <v>13048924896.17</v>
+      </c>
+      <c r="F570">
+        <v>28.92590326296187</v>
+      </c>
+      <c r="G570">
+        <v>10996862328.91</v>
+      </c>
+      <c r="H570">
+        <v>24.37704090208414</v>
+      </c>
+      <c r="I570">
+        <v>12427440661.93</v>
+      </c>
+      <c r="J570">
+        <v>27.54824242253826</v>
+      </c>
+      <c r="K570">
+        <v>5549377354.53</v>
+      </c>
+      <c r="L570">
+        <v>12.30145424271088</v>
+      </c>
+      <c r="M570" s="2">
+        <v>45915</v>
+      </c>
+    </row>
+    <row r="571" spans="1:13">
+      <c r="A571" t="s">
+        <v>584</v>
+      </c>
+      <c r="B571">
+        <v>39273569367.08</v>
+      </c>
+      <c r="C571">
+        <v>2380321603.84</v>
+      </c>
+      <c r="D571">
+        <v>6.060874125271739</v>
+      </c>
+      <c r="E571">
+        <v>12217984516.73</v>
+      </c>
+      <c r="F571">
+        <v>31.10994165702543</v>
+      </c>
+      <c r="G571">
+        <v>9262055933.65</v>
+      </c>
+      <c r="H571">
+        <v>23.58343303884588</v>
+      </c>
+      <c r="I571">
+        <v>10551441948.75</v>
+      </c>
+      <c r="J571">
+        <v>26.8665214768955</v>
+      </c>
+      <c r="K571">
+        <v>4861765364.11</v>
+      </c>
+      <c r="L571">
+        <v>12.37922970196145</v>
+      </c>
+      <c r="M571" s="2">
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="572" spans="1:13">
+      <c r="A572" t="s">
+        <v>585</v>
+      </c>
+      <c r="B572">
+        <v>40760946266.92</v>
+      </c>
+      <c r="C572">
+        <v>3216591663.6</v>
+      </c>
+      <c r="D572">
+        <v>7.891356698483865</v>
+      </c>
+      <c r="E572">
+        <v>11987529294.35</v>
+      </c>
+      <c r="F572">
+        <v>29.40934986114053</v>
+      </c>
+      <c r="G572">
+        <v>10316187937.56</v>
+      </c>
+      <c r="H572">
+        <v>25.30900011497578</v>
+      </c>
+      <c r="I572">
+        <v>10125733595.06</v>
+      </c>
+      <c r="J572">
+        <v>24.84175300728397</v>
+      </c>
+      <c r="K572">
+        <v>5114903776.35</v>
+      </c>
+      <c r="L572">
+        <v>12.54854031811587</v>
+      </c>
+      <c r="M572" s="2">
+        <v>45929</v>
+      </c>
+    </row>
+    <row r="573" spans="1:13">
+      <c r="A573" t="s">
+        <v>586</v>
+      </c>
+      <c r="B573">
+        <v>42784831942.31999</v>
+      </c>
+      <c r="C573">
+        <v>3982315366.39</v>
+      </c>
+      <c r="D573">
+        <v>9.307773773094924</v>
+      </c>
+      <c r="E573">
+        <v>11331908754.19</v>
+      </c>
+      <c r="F573">
+        <v>26.48580873115738</v>
+      </c>
+      <c r="G573">
+        <v>12620493033.46</v>
+      </c>
+      <c r="H573">
+        <v>29.49758701979761</v>
+      </c>
+      <c r="I573">
+        <v>9842920432.339998</v>
+      </c>
+      <c r="J573">
+        <v>23.00563070017348</v>
+      </c>
+      <c r="K573">
+        <v>5007194355.94</v>
+      </c>
+      <c r="L573">
+        <v>11.70319977577663</v>
+      </c>
+      <c r="M573" s="2">
+        <v>45936</v>
       </c>
     </row>
   </sheetData>
@@ -33360,54 +33708,54 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="B2" s="2">
-        <v>45894</v>
+        <v>45936</v>
       </c>
       <c r="C2">
-        <v>7369925503.28</v>
+        <v>11331908754.19</v>
       </c>
       <c r="D2">
-        <v>22623430018.15</v>
+        <v>42784831942.32</v>
       </c>
       <c r="E2">
-        <v>32.57651690025501</v>
+        <v>26.48580873115738</v>
       </c>
       <c r="F2">
-        <v>6450549914.901537</v>
+        <v>6517077251.12465</v>
       </c>
       <c r="G2">
-        <v>32.02690448267496</v>
+        <v>32.00646963235547</v>
       </c>
       <c r="H2">
         <v>61902442704.89</v>
